--- a/trades/by_strategy/breakout_and_retest.xlsx
+++ b/trades/by_strategy/breakout_and_retest.xlsx
@@ -538,7 +538,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -713,7 +713,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip</t>
+          <t>OR-30H Support Flip [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -774,22 +774,22 @@
         <v>195.3</v>
       </c>
       <c r="T2" s="6" t="n">
-        <v>11436</v>
+        <v>22872</v>
       </c>
       <c r="U2" s="6" t="n">
-        <v>12694</v>
+        <v>25389</v>
       </c>
       <c r="V2" s="7" t="n">
-        <v>1188</v>
+        <v>2424</v>
       </c>
       <c r="W2" s="8" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -978,22 +978,22 @@
         <v>162.23</v>
       </c>
       <c r="T4" s="6" t="n">
-        <v>11926</v>
+        <v>23851</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>10545</v>
+        <v>21090</v>
       </c>
       <c r="V4" s="17" t="n">
-        <v>-1448</v>
+        <v>-2849</v>
       </c>
       <c r="W4" s="18" t="n">
-        <v>-12.1</v>
+        <v>-11.9</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 1 (General]</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="P5" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22900 PE</t>
+          <t>NIFTY 22850 PE</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
@@ -1074,28 +1074,28 @@
         </is>
       </c>
       <c r="R5" s="11" t="n">
-        <v>195.25</v>
+        <v>170.75</v>
       </c>
       <c r="S5" s="11" t="n">
-        <v>194.88</v>
+        <v>170.38</v>
       </c>
       <c r="T5" s="13" t="n">
-        <v>12691</v>
+        <v>33296</v>
       </c>
       <c r="U5" s="13" t="n">
-        <v>12667</v>
+        <v>33224</v>
       </c>
       <c r="V5" s="20" t="n">
-        <v>-95</v>
+        <v>-181</v>
       </c>
       <c r="W5" s="21" t="n">
-        <v>-0.7</v>
+        <v>-0.5</v>
       </c>
       <c r="X5" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="Z5" s="10" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 1 (General]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22950 PE</t>
+          <t>NIFTY 22900 PE</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1176,28 +1176,28 @@
         </is>
       </c>
       <c r="R6" s="4" t="n">
-        <v>194.4</v>
+        <v>170.04</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>193.99</v>
+        <v>169.63</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>25272</v>
+        <v>33158</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>25219</v>
+        <v>33078</v>
       </c>
       <c r="V6" s="17" t="n">
-        <v>-147</v>
+        <v>-189</v>
       </c>
       <c r="W6" s="18" t="n">
         <v>-0.6</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>PDH Support Flip</t>
+          <t>PDH Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23100 CE</t>
+          <t>NIFTY 23200 CE</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="R7" s="11" t="n">
-        <v>115.13</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>131.37</v>
+        <v>85.19</v>
       </c>
       <c r="T7" s="13" t="n">
-        <v>14967</v>
+        <v>9536</v>
       </c>
       <c r="U7" s="13" t="n">
-        <v>17078</v>
+        <v>11075</v>
       </c>
       <c r="V7" s="14" t="n">
-        <v>2033</v>
+        <v>1472</v>
       </c>
       <c r="W7" s="15" t="n">
-        <v>13.6</v>
+        <v>15.4</v>
       </c>
       <c r="X7" s="9" t="n">
         <v>2</v>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip</t>
+          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23100 CE</t>
+          <t>NIFTY 23200 CE</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1380,22 +1380,22 @@
         </is>
       </c>
       <c r="R8" s="4" t="n">
-        <v>125.68</v>
+        <v>81.22</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>107.23</v>
+        <v>67.58</v>
       </c>
       <c r="T8" s="6" t="n">
-        <v>16338</v>
+        <v>10559</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>13940</v>
+        <v>8785</v>
       </c>
       <c r="V8" s="17" t="n">
-        <v>-2473</v>
+        <v>-1838</v>
       </c>
       <c r="W8" s="18" t="n">
-        <v>-15.1</v>
+        <v>-17.4</v>
       </c>
       <c r="X8" s="2" t="n">
         <v>2</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>PDH Support Flip</t>
+          <t>PDH Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P9" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22800 CE</t>
+          <t>NIFTY 22900 CE</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
@@ -1482,28 +1482,28 @@
         </is>
       </c>
       <c r="R9" s="11" t="n">
-        <v>137.01</v>
+        <v>94.22</v>
       </c>
       <c r="S9" s="11" t="n">
-        <v>217.9</v>
+        <v>159.33</v>
       </c>
       <c r="T9" s="13" t="n">
-        <v>8906</v>
+        <v>12249</v>
       </c>
       <c r="U9" s="13" t="n">
-        <v>14164</v>
+        <v>20713</v>
       </c>
       <c r="V9" s="14" t="n">
-        <v>5187</v>
+        <v>8382</v>
       </c>
       <c r="W9" s="15" t="n">
-        <v>58.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="X9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z9" s="10" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22500 PE</t>
+          <t>NIFTY 22400 PE</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1584,28 +1584,28 @@
         </is>
       </c>
       <c r="R10" s="4" t="n">
-        <v>71.77</v>
+        <v>33.27</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>83.88</v>
+        <v>40.3</v>
       </c>
       <c r="T10" s="6" t="n">
-        <v>9330</v>
+        <v>6488</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>10904</v>
+        <v>7858</v>
       </c>
       <c r="V10" s="7" t="n">
-        <v>1508</v>
+        <v>1310</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>16.2</v>
+        <v>20.2</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip</t>
+          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22500 CE</t>
+          <t>NIFTY 22600 CE</t>
         </is>
       </c>
       <c r="Q11" s="9" t="inlineStr">
@@ -1686,28 +1686,28 @@
         </is>
       </c>
       <c r="R11" s="11" t="n">
-        <v>138.73</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="S11" s="11" t="n">
-        <v>171.78</v>
+        <v>121.92</v>
       </c>
       <c r="T11" s="13" t="n">
-        <v>9017</v>
+        <v>12518</v>
       </c>
       <c r="U11" s="13" t="n">
-        <v>11166</v>
+        <v>15850</v>
       </c>
       <c r="V11" s="14" t="n">
-        <v>2081</v>
+        <v>3257</v>
       </c>
       <c r="W11" s="15" t="n">
-        <v>23.1</v>
+        <v>26</v>
       </c>
       <c r="X11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z11" s="10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22450 PE</t>
+          <t>NIFTY 22350 PE</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1788,28 +1788,28 @@
         </is>
       </c>
       <c r="R12" s="4" t="n">
-        <v>145.25</v>
+        <v>100.98</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>222.17</v>
+        <v>163.09</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>9441</v>
+        <v>13127</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>14441</v>
+        <v>21202</v>
       </c>
       <c r="V12" s="7" t="n">
-        <v>4928</v>
+        <v>7991</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>52.2</v>
+        <v>60.9</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="P13" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22500 PE</t>
+          <t>NIFTY 22400 PE</t>
         </is>
       </c>
       <c r="Q13" s="9" t="inlineStr">
@@ -1890,28 +1890,28 @@
         </is>
       </c>
       <c r="R13" s="11" t="n">
-        <v>147.5</v>
+        <v>102.9</v>
       </c>
       <c r="S13" s="11" t="n">
-        <v>170.81</v>
+        <v>121.28</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>9588</v>
+        <v>13377</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>11103</v>
+        <v>15766</v>
       </c>
       <c r="V13" s="14" t="n">
-        <v>1448</v>
+        <v>2314</v>
       </c>
       <c r="W13" s="15" t="n">
-        <v>15.1</v>
+        <v>17.3</v>
       </c>
       <c r="X13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z13" s="10" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 1 (General]</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22550 PE</t>
+          <t>NIFTY 22500 PE</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1992,28 +1992,28 @@
         </is>
       </c>
       <c r="R14" s="4" t="n">
-        <v>153.06</v>
+        <v>129.62</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>128.78</v>
+        <v>107.95</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>9949</v>
+        <v>16851</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>8371</v>
+        <v>14034</v>
       </c>
       <c r="V14" s="17" t="n">
-        <v>-1642</v>
+        <v>-2892</v>
       </c>
       <c r="W14" s="18" t="n">
-        <v>-16.5</v>
+        <v>-17.2</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip</t>
+          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22650 CE</t>
+          <t>NIFTY 22750 CE</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2196,28 +2196,28 @@
         </is>
       </c>
       <c r="R16" s="4" t="n">
-        <v>192.09</v>
+        <v>146.03</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>172.33</v>
+        <v>129.6</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>24972</v>
+        <v>37968</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>22403</v>
+        <v>33696</v>
       </c>
       <c r="V16" s="17" t="n">
-        <v>-2659</v>
+        <v>-4384</v>
       </c>
       <c r="W16" s="18" t="n">
-        <v>-10.6</v>
+        <v>-11.5</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>PDH Support Flip</t>
+          <t>PDH Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22650 CE</t>
+          <t>NIFTY 22750 CE</t>
         </is>
       </c>
       <c r="Q17" s="9" t="inlineStr">
@@ -2298,28 +2298,28 @@
         </is>
       </c>
       <c r="R17" s="11" t="n">
-        <v>184.24</v>
+        <v>139.49</v>
       </c>
       <c r="S17" s="11" t="n">
-        <v>202.73</v>
+        <v>154.79</v>
       </c>
       <c r="T17" s="13" t="n">
-        <v>23951</v>
+        <v>36267</v>
       </c>
       <c r="U17" s="13" t="n">
-        <v>26355</v>
+        <v>40245</v>
       </c>
       <c r="V17" s="14" t="n">
-        <v>2309</v>
+        <v>3858</v>
       </c>
       <c r="W17" s="15" t="n">
-        <v>9.6</v>
+        <v>10.6</v>
       </c>
       <c r="X17" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y17" s="9" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z17" s="10" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 1 (General]</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22500 PE</t>
+          <t>NIFTY 22450 PE</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2400,28 +2400,28 @@
         </is>
       </c>
       <c r="R18" s="4" t="n">
-        <v>150.75</v>
+        <v>126.18</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>236.79</v>
+        <v>204.29</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>9799</v>
+        <v>16403</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>15391</v>
+        <v>26558</v>
       </c>
       <c r="V18" s="7" t="n">
-        <v>5519</v>
+        <v>10062</v>
       </c>
       <c r="W18" s="8" t="n">
-        <v>56.3</v>
+        <v>61.3</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22850 PE</t>
+          <t>NIFTY 22750 PE</t>
         </is>
       </c>
       <c r="Q19" s="9" t="inlineStr">
@@ -2502,28 +2502,28 @@
         </is>
       </c>
       <c r="R19" s="11" t="n">
-        <v>69.90000000000001</v>
+        <v>29.08</v>
       </c>
       <c r="S19" s="11" t="n">
-        <v>88.03</v>
+        <v>37.52</v>
       </c>
       <c r="T19" s="13" t="n">
-        <v>9087</v>
+        <v>5671</v>
       </c>
       <c r="U19" s="13" t="n">
-        <v>11444</v>
+        <v>7316</v>
       </c>
       <c r="V19" s="14" t="n">
-        <v>2289</v>
+        <v>1586</v>
       </c>
       <c r="W19" s="15" t="n">
-        <v>25.2</v>
+        <v>28</v>
       </c>
       <c r="X19" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y19" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z19" s="10" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip</t>
+          <t>OR-30H Support Flip [Tier 1 (General]</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23450 CE</t>
+          <t>NIFTY 23500 CE</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2604,22 +2604,22 @@
         </is>
       </c>
       <c r="R20" s="4" t="n">
-        <v>128.95</v>
+        <v>106.14</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>116.5</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>16764</v>
+        <v>13798</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>15145</v>
+        <v>12359</v>
       </c>
       <c r="V20" s="17" t="n">
-        <v>-1695</v>
+        <v>-1510</v>
       </c>
       <c r="W20" s="18" t="n">
-        <v>-10.1</v>
+        <v>-10.9</v>
       </c>
       <c r="X20" s="2" t="n">
         <v>2</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23400 PE</t>
+          <t>NIFTY 23300 PE</t>
         </is>
       </c>
       <c r="Q21" s="9" t="inlineStr">
@@ -2706,28 +2706,28 @@
         </is>
       </c>
       <c r="R21" s="11" t="n">
-        <v>155.93</v>
+        <v>109.2</v>
       </c>
       <c r="S21" s="11" t="n">
-        <v>193.44</v>
+        <v>139.1</v>
       </c>
       <c r="T21" s="13" t="n">
-        <v>10135</v>
+        <v>28392</v>
       </c>
       <c r="U21" s="13" t="n">
-        <v>12574</v>
+        <v>36166</v>
       </c>
       <c r="V21" s="14" t="n">
-        <v>2369</v>
+        <v>7663</v>
       </c>
       <c r="W21" s="15" t="n">
-        <v>23.4</v>
+        <v>27</v>
       </c>
       <c r="X21" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y21" s="9" t="n">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="Z21" s="10" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>PDH Support Flip</t>
+          <t>PDH Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23400 CE</t>
+          <t>NIFTY 23500 CE</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2808,28 +2808,28 @@
         </is>
       </c>
       <c r="R22" s="4" t="n">
-        <v>62.35</v>
+        <v>24.77</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>46.34</v>
+        <v>16.54</v>
       </c>
       <c r="T22" s="6" t="n">
-        <v>8106</v>
+        <v>6440</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>6024</v>
+        <v>4300</v>
       </c>
       <c r="V22" s="17" t="n">
-        <v>-2141</v>
+        <v>-2196</v>
       </c>
       <c r="W22" s="18" t="n">
-        <v>-26.4</v>
+        <v>-34.1</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 1 (General]</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="P23" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23200 PE</t>
+          <t>NIFTY 23150 PE</t>
         </is>
       </c>
       <c r="Q23" s="9" t="inlineStr">
@@ -2910,28 +2910,28 @@
         </is>
       </c>
       <c r="R23" s="11" t="n">
-        <v>156.61</v>
+        <v>132.84</v>
       </c>
       <c r="S23" s="11" t="n">
-        <v>171.48</v>
+        <v>146.21</v>
       </c>
       <c r="T23" s="13" t="n">
-        <v>20359</v>
+        <v>25904</v>
       </c>
       <c r="U23" s="13" t="n">
-        <v>22292</v>
+        <v>28511</v>
       </c>
       <c r="V23" s="14" t="n">
-        <v>1845</v>
+        <v>2508</v>
       </c>
       <c r="W23" s="15" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y23" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z23" s="10" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23400 PE</t>
+          <t>NIFTY 23300 PE</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3012,28 +3012,28 @@
         </is>
       </c>
       <c r="R24" s="4" t="n">
-        <v>164.16</v>
+        <v>118.2</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>181.37</v>
+        <v>132.06</v>
       </c>
       <c r="T24" s="6" t="n">
-        <v>21341</v>
+        <v>30732</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>23578</v>
+        <v>34336</v>
       </c>
       <c r="V24" s="7" t="n">
-        <v>2147</v>
+        <v>3494</v>
       </c>
       <c r="W24" s="8" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip</t>
+          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="P25" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23300 CE</t>
+          <t>NIFTY 23400 CE</t>
         </is>
       </c>
       <c r="Q25" s="9" t="inlineStr">
@@ -3114,28 +3114,28 @@
         </is>
       </c>
       <c r="R25" s="11" t="n">
-        <v>116.52</v>
+        <v>73.81</v>
       </c>
       <c r="S25" s="11" t="n">
-        <v>139.02</v>
+        <v>90.41</v>
       </c>
       <c r="T25" s="13" t="n">
-        <v>15148</v>
+        <v>14393</v>
       </c>
       <c r="U25" s="13" t="n">
-        <v>18073</v>
+        <v>17630</v>
       </c>
       <c r="V25" s="14" t="n">
-        <v>2846</v>
+        <v>3158</v>
       </c>
       <c r="W25" s="15" t="n">
-        <v>18.8</v>
+        <v>21.9</v>
       </c>
       <c r="X25" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y25" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z25" s="10" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23400 PE</t>
+          <t>NIFTY 23300 PE</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3216,28 +3216,28 @@
         </is>
       </c>
       <c r="R26" s="4" t="n">
-        <v>127.87</v>
+        <v>84.7</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>105.88</v>
+        <v>68.17</v>
       </c>
       <c r="T26" s="6" t="n">
-        <v>8312</v>
+        <v>11011</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>6882</v>
+        <v>8862</v>
       </c>
       <c r="V26" s="17" t="n">
-        <v>-1490</v>
+        <v>-2214</v>
       </c>
       <c r="W26" s="18" t="n">
-        <v>-17.9</v>
+        <v>-20.1</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="P27" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23400 PE</t>
+          <t>NIFTY 23300 PE</t>
         </is>
       </c>
       <c r="Q27" s="9" t="inlineStr">
@@ -3318,28 +3318,28 @@
         </is>
       </c>
       <c r="R27" s="11" t="n">
-        <v>124.37</v>
+        <v>82.19</v>
       </c>
       <c r="S27" s="11" t="n">
-        <v>109.25</v>
+        <v>70.87</v>
       </c>
       <c r="T27" s="13" t="n">
-        <v>16168</v>
+        <v>16027</v>
       </c>
       <c r="U27" s="13" t="n">
-        <v>14202</v>
+        <v>13820</v>
       </c>
       <c r="V27" s="20" t="n">
-        <v>-2040</v>
+        <v>-2281</v>
       </c>
       <c r="W27" s="21" t="n">
-        <v>-12.6</v>
+        <v>-14.2</v>
       </c>
       <c r="X27" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y27" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z27" s="10" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip</t>
+          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23550 CE</t>
+          <t>NIFTY 23650 CE</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3420,22 +3420,22 @@
         </is>
       </c>
       <c r="R28" s="4" t="n">
-        <v>130.25</v>
+        <v>87.92</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>111.71</v>
+        <v>73.78</v>
       </c>
       <c r="T28" s="6" t="n">
-        <v>16932</v>
+        <v>11430</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>14522</v>
+        <v>9591</v>
       </c>
       <c r="V28" s="17" t="n">
-        <v>-2485</v>
+        <v>-1904</v>
       </c>
       <c r="W28" s="18" t="n">
-        <v>-14.7</v>
+        <v>-16.7</v>
       </c>
       <c r="X28" s="2" t="n">
         <v>2</v>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P29" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23650 PE</t>
+          <t>NIFTY 23550 PE</t>
         </is>
       </c>
       <c r="Q29" s="9" t="inlineStr">
@@ -3522,28 +3522,28 @@
         </is>
       </c>
       <c r="R29" s="11" t="n">
-        <v>138.47</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="S29" s="11" t="n">
-        <v>147.31</v>
+        <v>102.14</v>
       </c>
       <c r="T29" s="13" t="n">
-        <v>9001</v>
+        <v>24848</v>
       </c>
       <c r="U29" s="13" t="n">
-        <v>9575</v>
+        <v>26556</v>
       </c>
       <c r="V29" s="14" t="n">
-        <v>510</v>
+        <v>1612</v>
       </c>
       <c r="W29" s="15" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="X29" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y29" s="9" t="n">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="Z29" s="10" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23800 PE</t>
+          <t>NIFTY 23700 PE</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3624,28 +3624,28 @@
         </is>
       </c>
       <c r="R30" s="4" t="n">
-        <v>60.25</v>
+        <v>22.37</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>83.19</v>
+        <v>33.47</v>
       </c>
       <c r="T30" s="6" t="n">
-        <v>7832</v>
+        <v>5816</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>10815</v>
+        <v>8702</v>
       </c>
       <c r="V30" s="7" t="n">
-        <v>2916</v>
+        <v>2824</v>
       </c>
       <c r="W30" s="8" t="n">
-        <v>37.2</v>
+        <v>48.6</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y30" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip</t>
+          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="P31" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23950 CE</t>
+          <t>NIFTY 24050 CE</t>
         </is>
       </c>
       <c r="Q31" s="9" t="inlineStr">
@@ -3726,22 +3726,22 @@
         </is>
       </c>
       <c r="R31" s="11" t="n">
-        <v>123.41</v>
+        <v>78.55</v>
       </c>
       <c r="S31" s="11" t="n">
-        <v>122.49</v>
+        <v>77.67</v>
       </c>
       <c r="T31" s="13" t="n">
-        <v>16043</v>
+        <v>10212</v>
       </c>
       <c r="U31" s="13" t="n">
-        <v>15924</v>
+        <v>10097</v>
       </c>
       <c r="V31" s="20" t="n">
-        <v>-196</v>
+        <v>-180</v>
       </c>
       <c r="W31" s="21" t="n">
-        <v>-1.2</v>
+        <v>-1.8</v>
       </c>
       <c r="X31" s="9" t="n">
         <v>2</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23950 PE</t>
+          <t>NIFTY 23850 PE</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3828,28 +3828,28 @@
         </is>
       </c>
       <c r="R32" s="4" t="n">
-        <v>142.38</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>163</v>
+        <v>111.26</v>
       </c>
       <c r="T32" s="6" t="n">
-        <v>9255</v>
+        <v>12434</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>10595</v>
+        <v>14464</v>
       </c>
       <c r="V32" s="7" t="n">
-        <v>1274</v>
+        <v>1956</v>
       </c>
       <c r="W32" s="8" t="n">
-        <v>13.8</v>
+        <v>15.7</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y32" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 1 (General]</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="P33" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24000 PE</t>
+          <t>NIFTY 23950 PE</t>
         </is>
       </c>
       <c r="Q33" s="9" t="inlineStr">
@@ -3930,28 +3930,28 @@
         </is>
       </c>
       <c r="R33" s="11" t="n">
-        <v>159.9</v>
+        <v>134.93</v>
       </c>
       <c r="S33" s="11" t="n">
-        <v>164.09</v>
+        <v>138.65</v>
       </c>
       <c r="T33" s="13" t="n">
-        <v>20787</v>
+        <v>26311</v>
       </c>
       <c r="U33" s="13" t="n">
-        <v>21332</v>
+        <v>27037</v>
       </c>
       <c r="V33" s="14" t="n">
-        <v>458</v>
+        <v>628</v>
       </c>
       <c r="W33" s="15" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="X33" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y33" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z33" s="10" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip</t>
+          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24100 CE</t>
+          <t>NIFTY 24200 CE</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4032,28 +4032,28 @@
         </is>
       </c>
       <c r="R34" s="4" t="n">
-        <v>154.44</v>
+        <v>109.25</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>134.15</v>
+        <v>93.11</v>
       </c>
       <c r="T34" s="6" t="n">
-        <v>20077</v>
+        <v>28405</v>
       </c>
       <c r="U34" s="6" t="n">
-        <v>17440</v>
+        <v>24209</v>
       </c>
       <c r="V34" s="17" t="n">
-        <v>-2718</v>
+        <v>-4290</v>
       </c>
       <c r="W34" s="18" t="n">
-        <v>-13.5</v>
+        <v>-15.1</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="P35" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24000 PE</t>
+          <t>NIFTY 23900 PE</t>
         </is>
       </c>
       <c r="Q35" s="9" t="inlineStr">
@@ -4134,28 +4134,28 @@
         </is>
       </c>
       <c r="R35" s="11" t="n">
-        <v>50.61</v>
+        <v>17.87</v>
       </c>
       <c r="S35" s="11" t="n">
-        <v>36.47</v>
+        <v>11.25</v>
       </c>
       <c r="T35" s="13" t="n">
-        <v>6579</v>
+        <v>4646</v>
       </c>
       <c r="U35" s="13" t="n">
-        <v>4741</v>
+        <v>2925</v>
       </c>
       <c r="V35" s="20" t="n">
-        <v>-1895</v>
+        <v>-1775</v>
       </c>
       <c r="W35" s="21" t="n">
-        <v>-28.8</v>
+        <v>-38.2</v>
       </c>
       <c r="X35" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y35" s="9" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z35" s="10" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24050 PE</t>
+          <t>NIFTY 23950 PE</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4236,28 +4236,28 @@
         </is>
       </c>
       <c r="R36" s="4" t="n">
-        <v>63.5</v>
+        <v>24.47</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>61.03</v>
+        <v>22.45</v>
       </c>
       <c r="T36" s="6" t="n">
-        <v>4128</v>
+        <v>4772</v>
       </c>
       <c r="U36" s="6" t="n">
-        <v>3967</v>
+        <v>4378</v>
       </c>
       <c r="V36" s="17" t="n">
-        <v>-215</v>
+        <v>-449</v>
       </c>
       <c r="W36" s="18" t="n">
-        <v>-5.2</v>
+        <v>-9.4</v>
       </c>
       <c r="X36" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y36" s="2" t="n">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 1 (General]</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="P37" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24100 PE</t>
+          <t>NIFTY 24050 PE</t>
         </is>
       </c>
       <c r="Q37" s="9" t="inlineStr">
@@ -4338,22 +4338,22 @@
         </is>
       </c>
       <c r="R37" s="11" t="n">
-        <v>122.02</v>
+        <v>97.47</v>
       </c>
       <c r="S37" s="11" t="n">
-        <v>105.43</v>
+        <v>83.11</v>
       </c>
       <c r="T37" s="13" t="n">
-        <v>15863</v>
+        <v>12671</v>
       </c>
       <c r="U37" s="13" t="n">
-        <v>13706</v>
+        <v>10804</v>
       </c>
       <c r="V37" s="20" t="n">
-        <v>-2230</v>
+        <v>-1935</v>
       </c>
       <c r="W37" s="21" t="n">
-        <v>-14.1</v>
+        <v>-15.3</v>
       </c>
       <c r="X37" s="9" t="n">
         <v>2</v>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24150 PE</t>
+          <t>NIFTY 24050 PE</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4440,28 +4440,28 @@
         </is>
       </c>
       <c r="R38" s="4" t="n">
-        <v>112.26</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>111.33</v>
+        <v>70.09</v>
       </c>
       <c r="T38" s="6" t="n">
-        <v>14594</v>
+        <v>13837</v>
       </c>
       <c r="U38" s="6" t="n">
-        <v>14473</v>
+        <v>13668</v>
       </c>
       <c r="V38" s="17" t="n">
-        <v>-195</v>
+        <v>-242</v>
       </c>
       <c r="W38" s="18" t="n">
-        <v>-1.3</v>
+        <v>-1.7</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y38" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="P39" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24200 PE</t>
+          <t>NIFTY 24100 PE</t>
         </is>
       </c>
       <c r="Q39" s="9" t="inlineStr">
@@ -4542,22 +4542,22 @@
         </is>
       </c>
       <c r="R39" s="11" t="n">
-        <v>123.77</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="S39" s="11" t="n">
-        <v>144.31</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T39" s="13" t="n">
-        <v>16090</v>
+        <v>10344</v>
       </c>
       <c r="U39" s="13" t="n">
-        <v>18760</v>
+        <v>12337</v>
       </c>
       <c r="V39" s="14" t="n">
-        <v>2589</v>
+        <v>1924</v>
       </c>
       <c r="W39" s="15" t="n">
-        <v>16.1</v>
+        <v>18.6</v>
       </c>
       <c r="X39" s="9" t="n">
         <v>2</v>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24300 PE</t>
+          <t>NIFTY 24200 PE</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4644,22 +4644,22 @@
         </is>
       </c>
       <c r="R40" s="4" t="n">
-        <v>138.12</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>150.48</v>
+        <v>103.12</v>
       </c>
       <c r="T40" s="6" t="n">
-        <v>17956</v>
+        <v>12200</v>
       </c>
       <c r="U40" s="6" t="n">
-        <v>19562</v>
+        <v>13406</v>
       </c>
       <c r="V40" s="7" t="n">
-        <v>1524</v>
+        <v>1134</v>
       </c>
       <c r="W40" s="8" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X40" s="2" t="n">
         <v>2</v>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>PDH Support Flip</t>
+          <t>PDH Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="P41" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24350 CE</t>
+          <t>NIFTY 24450 CE</t>
         </is>
       </c>
       <c r="Q41" s="9" t="inlineStr">
@@ -4746,22 +4746,22 @@
         </is>
       </c>
       <c r="R41" s="11" t="n">
-        <v>151.85</v>
+        <v>105.33</v>
       </c>
       <c r="S41" s="11" t="n">
-        <v>133.61</v>
+        <v>91.06</v>
       </c>
       <c r="T41" s="13" t="n">
-        <v>19740</v>
+        <v>13693</v>
       </c>
       <c r="U41" s="13" t="n">
-        <v>17369</v>
+        <v>11838</v>
       </c>
       <c r="V41" s="20" t="n">
-        <v>-2452</v>
+        <v>-1925</v>
       </c>
       <c r="W41" s="21" t="n">
-        <v>-12.4</v>
+        <v>-14.1</v>
       </c>
       <c r="X41" s="9" t="n">
         <v>2</v>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24150 PE</t>
+          <t>NIFTY 24050 PE</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -4848,28 +4848,28 @@
         </is>
       </c>
       <c r="R42" s="4" t="n">
-        <v>162.35</v>
+        <v>115.9</v>
       </c>
       <c r="S42" s="4" t="n">
-        <v>145.17</v>
+        <v>102.09</v>
       </c>
       <c r="T42" s="6" t="n">
-        <v>21106</v>
+        <v>30134</v>
       </c>
       <c r="U42" s="6" t="n">
-        <v>18872</v>
+        <v>26543</v>
       </c>
       <c r="V42" s="17" t="n">
-        <v>-2317</v>
+        <v>-3689</v>
       </c>
       <c r="W42" s="18" t="n">
-        <v>-11</v>
+        <v>-12.2</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y42" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 1 (General]</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="P43" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24200 PE</t>
+          <t>NIFTY 24150 PE</t>
         </is>
       </c>
       <c r="Q43" s="9" t="inlineStr">
@@ -4950,22 +4950,22 @@
         </is>
       </c>
       <c r="R43" s="11" t="n">
-        <v>71.92</v>
+        <v>47.42</v>
       </c>
       <c r="S43" s="11" t="n">
-        <v>68.58</v>
+        <v>44.12</v>
       </c>
       <c r="T43" s="13" t="n">
-        <v>9350</v>
+        <v>6165</v>
       </c>
       <c r="U43" s="13" t="n">
-        <v>8915</v>
+        <v>5736</v>
       </c>
       <c r="V43" s="20" t="n">
-        <v>-498</v>
+        <v>-487</v>
       </c>
       <c r="W43" s="21" t="n">
-        <v>-5.3</v>
+        <v>-7.9</v>
       </c>
       <c r="X43" s="9" t="n">
         <v>2</v>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24250 PE</t>
+          <t>NIFTY 24150 PE</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5052,28 +5052,28 @@
         </is>
       </c>
       <c r="R44" s="4" t="n">
-        <v>65.41</v>
+        <v>26.03</v>
       </c>
       <c r="S44" s="4" t="n">
-        <v>105.01</v>
+        <v>47.95</v>
       </c>
       <c r="T44" s="6" t="n">
-        <v>4252</v>
+        <v>5076</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>6826</v>
+        <v>9350</v>
       </c>
       <c r="V44" s="7" t="n">
-        <v>2515</v>
+        <v>4212</v>
       </c>
       <c r="W44" s="8" t="n">
-        <v>59.1</v>
+        <v>83</v>
       </c>
       <c r="X44" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y44" s="2" t="n">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="P45" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24050 PE</t>
+          <t>NIFTY 23950 PE</t>
         </is>
       </c>
       <c r="Q45" s="9" t="inlineStr">
@@ -5154,22 +5154,22 @@
         </is>
       </c>
       <c r="R45" s="11" t="n">
-        <v>146.62</v>
+        <v>100.92</v>
       </c>
       <c r="S45" s="11" t="n">
-        <v>129.18</v>
+        <v>87.36</v>
       </c>
       <c r="T45" s="13" t="n">
-        <v>19061</v>
+        <v>13120</v>
       </c>
       <c r="U45" s="13" t="n">
-        <v>16793</v>
+        <v>11357</v>
       </c>
       <c r="V45" s="20" t="n">
-        <v>-2347</v>
+        <v>-1832</v>
       </c>
       <c r="W45" s="21" t="n">
-        <v>-12.3</v>
+        <v>-14</v>
       </c>
       <c r="X45" s="9" t="n">
         <v>2</v>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24200 PE</t>
+          <t>NIFTY 24100 PE</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5256,28 +5256,28 @@
         </is>
       </c>
       <c r="R46" s="4" t="n">
-        <v>151.22</v>
+        <v>106.55</v>
       </c>
       <c r="S46" s="4" t="n">
-        <v>152.97</v>
+        <v>107.61</v>
       </c>
       <c r="T46" s="6" t="n">
-        <v>19659</v>
+        <v>27703</v>
       </c>
       <c r="U46" s="6" t="n">
-        <v>19886</v>
+        <v>27979</v>
       </c>
       <c r="V46" s="7" t="n">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="X46" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y46" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="P47" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24250 PE</t>
+          <t>NIFTY 24150 PE</t>
         </is>
       </c>
       <c r="Q47" s="9" t="inlineStr">
@@ -5358,28 +5358,28 @@
         </is>
       </c>
       <c r="R47" s="11" t="n">
-        <v>61.66</v>
+        <v>24.43</v>
       </c>
       <c r="S47" s="11" t="n">
-        <v>43.31</v>
+        <v>14.9</v>
       </c>
       <c r="T47" s="13" t="n">
-        <v>8016</v>
+        <v>6352</v>
       </c>
       <c r="U47" s="13" t="n">
-        <v>5630</v>
+        <v>3874</v>
       </c>
       <c r="V47" s="20" t="n">
-        <v>-2444</v>
+        <v>-2533</v>
       </c>
       <c r="W47" s="21" t="n">
-        <v>-30.5</v>
+        <v>-39.9</v>
       </c>
       <c r="X47" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y47" s="9" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z47" s="10" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24300 PE</t>
+          <t>NIFTY 24200 PE</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5460,28 +5460,28 @@
         </is>
       </c>
       <c r="R48" s="4" t="n">
-        <v>72.01000000000001</v>
+        <v>30.17</v>
       </c>
       <c r="S48" s="4" t="n">
-        <v>95.72</v>
+        <v>43.62</v>
       </c>
       <c r="T48" s="6" t="n">
-        <v>9361</v>
+        <v>5883</v>
       </c>
       <c r="U48" s="6" t="n">
-        <v>12444</v>
+        <v>8506</v>
       </c>
       <c r="V48" s="7" t="n">
-        <v>3013</v>
+        <v>2561</v>
       </c>
       <c r="W48" s="8" t="n">
-        <v>32.2</v>
+        <v>43.5</v>
       </c>
       <c r="X48" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y48" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -5670,22 +5670,22 @@
         <v>192.28</v>
       </c>
       <c r="T50" s="6" t="n">
-        <v>10555</v>
+        <v>21109</v>
       </c>
       <c r="U50" s="6" t="n">
-        <v>12498</v>
+        <v>24996</v>
       </c>
       <c r="V50" s="7" t="n">
-        <v>1874</v>
+        <v>3795</v>
       </c>
       <c r="W50" s="8" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="X50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y50" s="2" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="P51" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24450 PE</t>
+          <t>NIFTY 24350 PE</t>
         </is>
       </c>
       <c r="Q51" s="9" t="inlineStr">
@@ -5766,28 +5766,28 @@
         </is>
       </c>
       <c r="R51" s="11" t="n">
-        <v>166.64</v>
+        <v>121.22</v>
       </c>
       <c r="S51" s="11" t="n">
-        <v>163.36</v>
+        <v>118.25</v>
       </c>
       <c r="T51" s="13" t="n">
-        <v>10832</v>
+        <v>31517</v>
       </c>
       <c r="U51" s="13" t="n">
-        <v>10618</v>
+        <v>30745</v>
       </c>
       <c r="V51" s="20" t="n">
-        <v>-280</v>
+        <v>-877</v>
       </c>
       <c r="W51" s="21" t="n">
-        <v>-2.6</v>
+        <v>-2.8</v>
       </c>
       <c r="X51" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y51" s="9" t="n">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="Z51" s="10" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24500 PE</t>
+          <t>NIFTY 24400 PE</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -5868,28 +5868,28 @@
         </is>
       </c>
       <c r="R52" s="4" t="n">
-        <v>177.88</v>
+        <v>130.53</v>
       </c>
       <c r="S52" s="4" t="n">
-        <v>196.35</v>
+        <v>145.5</v>
       </c>
       <c r="T52" s="6" t="n">
-        <v>23124</v>
+        <v>33938</v>
       </c>
       <c r="U52" s="6" t="n">
-        <v>25526</v>
+        <v>37830</v>
       </c>
       <c r="V52" s="7" t="n">
-        <v>2308</v>
+        <v>3776</v>
       </c>
       <c r="W52" s="8" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="X52" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y52" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -5976,22 +5976,22 @@
         <v>142.15</v>
       </c>
       <c r="T53" s="13" t="n">
-        <v>10720</v>
+        <v>21440</v>
       </c>
       <c r="U53" s="13" t="n">
-        <v>9240</v>
+        <v>18480</v>
       </c>
       <c r="V53" s="20" t="n">
-        <v>-1545</v>
+        <v>-3043</v>
       </c>
       <c r="W53" s="21" t="n">
-        <v>-14.4</v>
+        <v>-14.2</v>
       </c>
       <c r="X53" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y53" s="9" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="Z53" s="10" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip</t>
+          <t>PDL Resistance Flip [Tier 1 (General]</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24500 PE</t>
+          <t>NIFTY 24450 PE</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6072,28 +6072,28 @@
         </is>
       </c>
       <c r="R54" s="4" t="n">
-        <v>166.12</v>
+        <v>141.85</v>
       </c>
       <c r="S54" s="4" t="n">
-        <v>181.47</v>
+        <v>155.69</v>
       </c>
       <c r="T54" s="6" t="n">
-        <v>21596</v>
+        <v>27661</v>
       </c>
       <c r="U54" s="6" t="n">
-        <v>23591</v>
+        <v>30360</v>
       </c>
       <c r="V54" s="7" t="n">
-        <v>1905</v>
+        <v>2596</v>
       </c>
       <c r="W54" s="8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="X54" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y54" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z54" s="3" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip</t>
+          <t>OR-30L Resistance Flip [Tier 1 (General]</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="P55" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24550 PE</t>
+          <t>NIFTY 24500 PE</t>
         </is>
       </c>
       <c r="Q55" s="9" t="inlineStr">
@@ -6174,28 +6174,28 @@
         </is>
       </c>
       <c r="R55" s="11" t="n">
-        <v>154.52</v>
+        <v>131.48</v>
       </c>
       <c r="S55" s="11" t="n">
-        <v>178.8</v>
+        <v>153.37</v>
       </c>
       <c r="T55" s="13" t="n">
-        <v>20088</v>
+        <v>25639</v>
       </c>
       <c r="U55" s="13" t="n">
-        <v>23244</v>
+        <v>29907</v>
       </c>
       <c r="V55" s="14" t="n">
-        <v>3067</v>
+        <v>4168</v>
       </c>
       <c r="W55" s="15" t="n">
-        <v>15.3</v>
+        <v>16.3</v>
       </c>
       <c r="X55" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y55" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z55" s="10" t="inlineStr">
         <is>

--- a/trades/by_strategy/breakout_and_retest.xlsx
+++ b/trades/by_strategy/breakout_and_retest.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip [Tier 3 (Expensive]</t>
+          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22700 CE</t>
+          <t>NIFTY 22800 CE</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -768,22 +768,22 @@
         </is>
       </c>
       <c r="R2" s="4" t="n">
-        <v>175.94</v>
+        <v>129.77</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>195.3</v>
+        <v>145.68</v>
       </c>
       <c r="T2" s="6" t="n">
-        <v>22872</v>
+        <v>16870</v>
       </c>
       <c r="U2" s="6" t="n">
-        <v>25389</v>
+        <v>18938</v>
       </c>
       <c r="V2" s="7" t="n">
-        <v>2424</v>
+        <v>1987</v>
       </c>
       <c r="W2" s="8" t="n">
-        <v>10.6</v>
+        <v>11.8</v>
       </c>
       <c r="X2" s="2" t="n">
         <v>2</v>
@@ -815,7 +815,7 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 3 (Expensive]</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="P3" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22800 PE</t>
+          <t>NIFTY 22700 PE</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="R3" s="11" t="n">
-        <v>165.38</v>
+        <v>121.21</v>
       </c>
       <c r="S3" s="11" t="n">
-        <v>215.48</v>
+        <v>162.55</v>
       </c>
       <c r="T3" s="13" t="n">
-        <v>21499</v>
+        <v>15757</v>
       </c>
       <c r="U3" s="13" t="n">
-        <v>28012</v>
+        <v>21132</v>
       </c>
       <c r="V3" s="14" t="n">
-        <v>6417</v>
+        <v>5290</v>
       </c>
       <c r="W3" s="15" t="n">
-        <v>29.8</v>
+        <v>33.6</v>
       </c>
       <c r="X3" s="9" t="n">
         <v>2</v>
@@ -917,7 +917,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22950 PE</t>
+          <t>NIFTY 22850 PE</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,22 +972,22 @@
         </is>
       </c>
       <c r="R4" s="4" t="n">
-        <v>183.47</v>
+        <v>136.34</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>162.23</v>
+        <v>118.95</v>
       </c>
       <c r="T4" s="6" t="n">
-        <v>23851</v>
+        <v>17724</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>21090</v>
+        <v>15464</v>
       </c>
       <c r="V4" s="17" t="n">
-        <v>-2849</v>
+        <v>-2338</v>
       </c>
       <c r="W4" s="18" t="n">
-        <v>-11.9</v>
+        <v>-13.2</v>
       </c>
       <c r="X4" s="2" t="n">
         <v>2</v>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="P15" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22600 PE</t>
+          <t>NIFTY 22550 PE</t>
         </is>
       </c>
       <c r="Q15" s="9" t="inlineStr">
@@ -2094,22 +2094,22 @@
         </is>
       </c>
       <c r="R15" s="11" t="n">
-        <v>170.5</v>
+        <v>145.36</v>
       </c>
       <c r="S15" s="11" t="n">
-        <v>152.11</v>
+        <v>128.78</v>
       </c>
       <c r="T15" s="13" t="n">
-        <v>22165</v>
+        <v>18897</v>
       </c>
       <c r="U15" s="13" t="n">
-        <v>19774</v>
+        <v>16741</v>
       </c>
       <c r="V15" s="20" t="n">
-        <v>-2476</v>
+        <v>-2235</v>
       </c>
       <c r="W15" s="21" t="n">
-        <v>-11.2</v>
+        <v>-11.8</v>
       </c>
       <c r="X15" s="9" t="n">
         <v>2</v>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="P49" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24400 PE</t>
+          <t>NIFTY 24300 PE</t>
         </is>
       </c>
       <c r="Q49" s="9" t="inlineStr">
@@ -5562,22 +5562,22 @@
         </is>
       </c>
       <c r="R49" s="11" t="n">
-        <v>162.85</v>
+        <v>115.25</v>
       </c>
       <c r="S49" s="11" t="n">
-        <v>214.25</v>
+        <v>157.06</v>
       </c>
       <c r="T49" s="13" t="n">
-        <v>21170</v>
+        <v>14982</v>
       </c>
       <c r="U49" s="13" t="n">
-        <v>27852</v>
+        <v>20418</v>
       </c>
       <c r="V49" s="14" t="n">
-        <v>6586</v>
+        <v>5353</v>
       </c>
       <c r="W49" s="15" t="n">
-        <v>31.1</v>
+        <v>35.7</v>
       </c>
       <c r="X49" s="9" t="n">
         <v>2</v>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 3 (Expensive]</t>
+          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24450 PE</t>
+          <t>NIFTY 24350 PE</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5664,22 +5664,22 @@
         </is>
       </c>
       <c r="R50" s="4" t="n">
-        <v>162.38</v>
+        <v>115.03</v>
       </c>
       <c r="S50" s="4" t="n">
-        <v>192.28</v>
+        <v>139.14</v>
       </c>
       <c r="T50" s="6" t="n">
-        <v>21109</v>
+        <v>14954</v>
       </c>
       <c r="U50" s="6" t="n">
-        <v>24996</v>
+        <v>18088</v>
       </c>
       <c r="V50" s="7" t="n">
-        <v>3795</v>
+        <v>3055</v>
       </c>
       <c r="W50" s="8" t="n">
-        <v>18</v>
+        <v>20.4</v>
       </c>
       <c r="X50" s="2" t="n">
         <v>2</v>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
+          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="P53" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24600 PE</t>
+          <t>NIFTY 24500 PE</t>
         </is>
       </c>
       <c r="Q53" s="9" t="inlineStr">
@@ -5970,22 +5970,22 @@
         </is>
       </c>
       <c r="R53" s="11" t="n">
-        <v>164.92</v>
+        <v>117.91</v>
       </c>
       <c r="S53" s="11" t="n">
-        <v>142.15</v>
+        <v>99.77</v>
       </c>
       <c r="T53" s="13" t="n">
-        <v>21440</v>
+        <v>15328</v>
       </c>
       <c r="U53" s="13" t="n">
-        <v>18480</v>
+        <v>12970</v>
       </c>
       <c r="V53" s="20" t="n">
-        <v>-3043</v>
+        <v>-2431</v>
       </c>
       <c r="W53" s="21" t="n">
-        <v>-14.2</v>
+        <v>-15.9</v>
       </c>
       <c r="X53" s="9" t="n">
         <v>2</v>

--- a/trades/by_strategy/breakout_and_retest.xlsx
+++ b/trades/by_strategy/breakout_and_retest.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Breakout &amp; Retest" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Breakout &amp; Retest'!$A$1:$Z$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Breakout &amp; Retest'!$A$1:$AA$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -96,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -143,6 +143,15 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -153,18 +162,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -532,22 +529,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z55"/>
+  <dimension ref="A1:AA56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
@@ -561,6 +558,7 @@
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="65" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -694,128 +692,130 @@
           <t>Rationale</t>
         </is>
       </c>
+      <c r="AA1" s="1" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+0.89R)</t>
+          <t>TRAILED (+0.28R)</t>
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>22712.95</v>
+        <v>24481.75</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>22671.3</v>
+        <v>24513.3</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>22900.38</v>
+        <v>24387.1</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>41.65</v>
+        <v>31.55</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>22749.9</v>
+        <v>24473</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N2" s="4" t="n">
-        <v>36.95</v>
+        <v>8.75</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>0.89</v>
+        <v>0.28</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22800 CE</t>
+          <t>NIFTY 24400 PE</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R2" s="4" t="n">
-        <v>129.77</v>
+        <v>130.53</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>145.68</v>
+        <v>133.96</v>
       </c>
       <c r="T2" s="6" t="n">
-        <v>16870</v>
+        <v>33938</v>
       </c>
       <c r="U2" s="6" t="n">
-        <v>18938</v>
+        <v>34830</v>
       </c>
       <c r="V2" s="7" t="n">
-        <v>1987</v>
+        <v>780</v>
       </c>
       <c r="W2" s="8" t="n">
-        <v>11.8</v>
+        <v>2.3</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>10:25 breakout: 5m high 22,742.50 cleared OR-30H 22,690.45 | 10:50 retest: 5m low 22,676.30 tested OR-30H 22,690.45 as support | 10:55 confirmation: 5m close 22,712.95 held above OR-30H and VWAP</t>
-        </is>
-      </c>
+          <t>09:20 breakdown: 5m low 24,501.00 breached PDL 24,511.30 | 09:25 retest: 5m high 24,506.35 tested PDL 24,511.30 as resistance | 09:40 confirmation: 5m close 24,481.75 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA2" s="3" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -825,201 +825,203 @@
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>TARGET HIT (3R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G3" s="11" t="n">
-        <v>22818.45</v>
+        <v>24452</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>22850.55</v>
+        <v>24496.85</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>22722.15</v>
+        <v>24317.45</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>32.1</v>
+        <v>44.85</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>22722.15</v>
+        <v>24447.65</v>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N3" s="11" t="n">
-        <v>96.3</v>
+        <v>4.35</v>
       </c>
       <c r="O3" s="12" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="P3" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22700 PE</t>
+          <t>NIFTY 24350 PE</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R3" s="11" t="n">
-        <v>121.21</v>
+        <v>121.22</v>
       </c>
       <c r="S3" s="11" t="n">
-        <v>162.55</v>
+        <v>122.7</v>
       </c>
       <c r="T3" s="13" t="n">
-        <v>15757</v>
+        <v>31517</v>
       </c>
       <c r="U3" s="13" t="n">
-        <v>21132</v>
+        <v>31902</v>
       </c>
       <c r="V3" s="14" t="n">
-        <v>5290</v>
+        <v>278</v>
       </c>
       <c r="W3" s="15" t="n">
-        <v>33.6</v>
+        <v>0.9</v>
       </c>
       <c r="X3" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y3" s="9" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z3" s="10" t="inlineStr">
         <is>
-          <t>11:40 breakdown: 5m low 22,839.70 breached PDL 22,845.25 | 11:45 retest: 5m high 22,841.90 tested PDL 22,845.25 as resistance | 11:55 confirmation: 5m close 22,818.45 held below PDL and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
-        </is>
-      </c>
+          <t>09:50 breakdown: 5m low 24,464.15 breached OR-30L 24,468.40 | 09:55 retest: 5m high 24,477.45 tested OR-30L 24,468.40 as resistance | 11:05 confirmation: 5m close 24,452.00 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA3" s="10" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PDL Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>TRAILED (+1.37R)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>24428.2</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>24468.5</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>24307.3</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>24373.1</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>STOPPED OUT (-1R)</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>22936.05</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>22979.15</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>22848.25</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>22979.15</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Structure Trail</t>
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>-43.1</v>
-      </c>
-      <c r="O4" s="16" t="n">
-        <v>-1</v>
+        <v>55.1</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>1.37</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22850 PE</t>
+          <t>NIFTY 24350 PE</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R4" s="4" t="n">
-        <v>136.34</v>
+        <v>115.03</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>118.95</v>
+        <v>139.14</v>
       </c>
       <c r="T4" s="6" t="n">
-        <v>17724</v>
+        <v>22431</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>15464</v>
-      </c>
-      <c r="V4" s="17" t="n">
-        <v>-2338</v>
-      </c>
-      <c r="W4" s="18" t="n">
-        <v>-13.2</v>
+        <v>27132</v>
+      </c>
+      <c r="V4" s="7" t="n">
+        <v>4606</v>
+      </c>
+      <c r="W4" s="8" t="n">
+        <v>20.5</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>10:10 breakdown: 5m low 22,950.90 breached OR-30L 22,981.35 | 10:15 retest: 5m high 22,974.15 tested OR-30L 22,981.35 as resistance | 10:20 confirmation: 5m close 22,936.05 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>09:20 breakdown: 5m low 24,390.90 breached PDL 24,429.25 | 09:25 retest: 5m high 24,430.90 tested PDL 24,429.25 as resistance | 09:40 confirmation: 5m close 24,428.20 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 1 (General]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -1029,67 +1031,67 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>TARGET HIT (3R)</t>
         </is>
       </c>
       <c r="G5" s="11" t="n">
-        <v>22891.95</v>
+        <v>24375.65</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>22932.2</v>
+        <v>24405.95</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>22771.2</v>
+        <v>24284.75</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>40.25</v>
+        <v>30.3</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>22891.95</v>
+        <v>24284.75</v>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>Breakeven</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="N5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="19" t="n">
-        <v>-0</v>
+        <v>90.90000000000001</v>
+      </c>
+      <c r="O5" s="12" t="n">
+        <v>2.5</v>
       </c>
       <c r="P5" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22850 PE</t>
+          <t>NIFTY 24300 PE</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R5" s="11" t="n">
-        <v>170.75</v>
+        <v>115.25</v>
       </c>
       <c r="S5" s="11" t="n">
-        <v>170.38</v>
+        <v>157.06</v>
       </c>
       <c r="T5" s="13" t="n">
-        <v>33296</v>
+        <v>22474</v>
       </c>
       <c r="U5" s="13" t="n">
-        <v>33224</v>
-      </c>
-      <c r="V5" s="20" t="n">
-        <v>-181</v>
-      </c>
-      <c r="W5" s="21" t="n">
-        <v>-0.5</v>
+        <v>30627</v>
+      </c>
+      <c r="V5" s="14" t="n">
+        <v>8052</v>
+      </c>
+      <c r="W5" s="15" t="n">
+        <v>35.8</v>
       </c>
       <c r="X5" s="9" t="n">
         <v>3</v>
@@ -1099,29 +1101,30 @@
       </c>
       <c r="Z5" s="10" t="inlineStr">
         <is>
-          <t>13:00 breakdown: 5m low 22,906.00 breached PDL 22,914.30 | 13:15 retest: 5m high 22,927.20 tested PDL 22,914.30 as resistance | 13:20 confirmation: 5m close 22,891.95 held below PDL and VWAP</t>
-        </is>
-      </c>
+          <t>10:00 breakdown: 5m low 24,376.55 breached OR-30L 24,390.90 | 10:05 retest: 5m high 24,379.50 tested OR-30L 24,390.90 as resistance | 10:45 confirmation: 5m close 24,375.65 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA5" s="10" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 1 (General]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1131,67 +1134,67 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>TRAILED (+1.24R)</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>22945.55</v>
+        <v>24283.85</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>22983.55</v>
+        <v>24317.45</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22831.55</v>
+        <v>24183.05</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>38</v>
+        <v>33.6</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>22945.55</v>
+        <v>24242.1</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>Breakeven</t>
+          <t>Structure Trail</t>
         </is>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="22" t="n">
-        <v>-0</v>
+        <v>41.75</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>1.24</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22900 PE</t>
+          <t>NIFTY 24200 PE</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R6" s="4" t="n">
-        <v>170.04</v>
+        <v>30.17</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>169.63</v>
+        <v>43.62</v>
       </c>
       <c r="T6" s="6" t="n">
-        <v>33158</v>
+        <v>5883</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>33078</v>
-      </c>
-      <c r="V6" s="17" t="n">
-        <v>-189</v>
-      </c>
-      <c r="W6" s="18" t="n">
-        <v>-0.6</v>
+        <v>8506</v>
+      </c>
+      <c r="V6" s="7" t="n">
+        <v>2561</v>
+      </c>
+      <c r="W6" s="8" t="n">
+        <v>43.5</v>
       </c>
       <c r="X6" s="2" t="n">
         <v>3</v>
@@ -1201,325 +1204,329 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>12:05 breakdown: 5m low 22,948.75 breached OR-30L 22,970.85 | 12:10 retest: 5m high 22,978.55 tested OR-30L 22,970.85 as resistance | 12:15 confirmation: 5m close 22,945.55 held below OR-30L and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
-        </is>
-      </c>
+          <t>09:20 breakdown: 5m low 24,283.05 breached PDL 24,298.35 | 09:25 retest: 5m high 24,310.20 tested PDL 24,298.35 as resistance | 10:00 confirmation: 5m close 24,283.85 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>PDH Support Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+0.99R)</t>
+          <t>TRAILED (+0.40R)</t>
         </is>
       </c>
       <c r="G7" s="11" t="n">
-        <v>23088.9</v>
+        <v>24252.8</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>23054.45</v>
+        <v>24288.9</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>23192.25</v>
+        <v>24144.5</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>34.45</v>
+        <v>36.1</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>23123.05</v>
+        <v>24238.2</v>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N7" s="11" t="n">
-        <v>34.15</v>
+        <v>14.6</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>0.99</v>
+        <v>0.4</v>
       </c>
       <c r="P7" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23200 CE</t>
+          <t>NIFTY 24150 PE</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="R7" s="11" t="n">
-        <v>73.34999999999999</v>
+        <v>24.43</v>
       </c>
       <c r="S7" s="11" t="n">
-        <v>85.19</v>
+        <v>27.85</v>
       </c>
       <c r="T7" s="13" t="n">
-        <v>9536</v>
+        <v>6352</v>
       </c>
       <c r="U7" s="13" t="n">
-        <v>11075</v>
+        <v>7241</v>
       </c>
       <c r="V7" s="14" t="n">
-        <v>1472</v>
+        <v>829</v>
       </c>
       <c r="W7" s="15" t="n">
-        <v>15.4</v>
+        <v>13.1</v>
       </c>
       <c r="X7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z7" s="10" t="inlineStr">
         <is>
-          <t>10:15 breakout: 5m high 23,094.60 cleared PDH 23,056.20 | 11:10 retest: 5m low 23,066.70 tested PDH 23,056.20 as support | 11:15 confirmation: 5m close 23,088.90 held above PDH and VWAP</t>
-        </is>
-      </c>
+          <t>10:15 breakdown: 5m low 24,277.40 breached OR-30L 24,281.45 | 10:20 retest: 5m high 24,283.90 tested OR-30L 24,281.45 as resistance | 10:25 confirmation: 5m close 24,252.80 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA7" s="10" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.27R)</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>23109.55</v>
+        <v>24204.75</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>23072.2</v>
+        <v>24238.4</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>23221.6</v>
+        <v>24103.8</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>37.35</v>
+        <v>33.65</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>23072.2</v>
+        <v>24195.75</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-37.35</v>
-      </c>
-      <c r="O8" s="16" t="n">
-        <v>-1</v>
+        <v>9</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>0.27</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23200 CE</t>
+          <t>NIFTY 24100 PE</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R8" s="4" t="n">
-        <v>81.22</v>
+        <v>106.55</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>67.58</v>
+        <v>109.85</v>
       </c>
       <c r="T8" s="6" t="n">
-        <v>10559</v>
+        <v>27703</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>8785</v>
-      </c>
-      <c r="V8" s="17" t="n">
-        <v>-1838</v>
-      </c>
-      <c r="W8" s="18" t="n">
-        <v>-17.4</v>
+        <v>28561</v>
+      </c>
+      <c r="V8" s="7" t="n">
+        <v>758</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>2.7</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>10:15 breakout: 5m high 23,094.60 cleared OR-30H 23,076.10 | 10:50 retest: 5m low 23,082.25 tested OR-30H 23,076.10 as support | 11:00 confirmation: 5m close 23,109.55 held above OR-30H and VWAP</t>
-        </is>
-      </c>
+          <t>10:05 breakdown: 5m low 24,213.00 breached PDL 24,226.95 | 10:10 retest: 5m high 24,228.40 tested PDL 24,226.95 as resistance | 10:50 confirmation: 5m close 24,204.75 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>PDH Support Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>TARGET HIT (3R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G9" s="11" t="n">
-        <v>22787.2</v>
+        <v>24041.2</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>22739.35</v>
+        <v>24076.25</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>22930.75</v>
+        <v>23936.05</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>47.85</v>
+        <v>35.05</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>22930.75</v>
+        <v>24052.45</v>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N9" s="11" t="n">
-        <v>143.55</v>
-      </c>
-      <c r="O9" s="12" t="n">
-        <v>2.5</v>
+        <v>-11.25</v>
+      </c>
+      <c r="O9" s="16" t="n">
+        <v>-0.32</v>
       </c>
       <c r="P9" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22900 CE</t>
+          <t>NIFTY 23950 PE</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R9" s="11" t="n">
-        <v>94.22</v>
+        <v>100.92</v>
       </c>
       <c r="S9" s="11" t="n">
-        <v>159.33</v>
+        <v>96.27</v>
       </c>
       <c r="T9" s="13" t="n">
-        <v>12249</v>
+        <v>19679</v>
       </c>
       <c r="U9" s="13" t="n">
-        <v>20713</v>
-      </c>
-      <c r="V9" s="14" t="n">
-        <v>8382</v>
-      </c>
-      <c r="W9" s="15" t="n">
-        <v>68.40000000000001</v>
+        <v>18773</v>
+      </c>
+      <c r="V9" s="17" t="n">
+        <v>-989</v>
+      </c>
+      <c r="W9" s="18" t="n">
+        <v>-5</v>
       </c>
       <c r="X9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y9" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z9" s="10" t="inlineStr">
         <is>
-          <t>09:35 breakout: 5m high 22,771.55 cleared PDH 22,757.80 | 09:40 retest: 5m low 22,748.55 tested PDH 22,757.80 as support | 09:50 confirmation: 5m close 22,787.20 held above PDH and VWAP</t>
-        </is>
-      </c>
+          <t>10:25 breakdown: 5m low 24,063.20 breached OR-30L 24,065.50 | 10:30 retest: 5m high 24,071.25 tested OR-30L 24,065.50 as resistance | 11:10 confirmation: 5m close 24,041.20 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA9" s="10" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1529,7 +1536,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1539,27 +1546,27 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+0.77R)</t>
+          <t>TRAILED (+1.39R)</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>22506.15</v>
+        <v>24242.9</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>22538.7</v>
+        <v>24292.7</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>22359.68</v>
+        <v>24093.5</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>32.55</v>
+        <v>49.8</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>22481.05</v>
+        <v>24173.6</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1568,38 +1575,38 @@
         </is>
       </c>
       <c r="N10" s="4" t="n">
-        <v>25.1</v>
+        <v>69.3</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>0.77</v>
+        <v>1.39</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22400 PE</t>
+          <t>NIFTY 24150 PE</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R10" s="4" t="n">
-        <v>33.27</v>
+        <v>26.03</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>40.3</v>
+        <v>47.95</v>
       </c>
       <c r="T10" s="6" t="n">
-        <v>6488</v>
+        <v>5076</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>7858</v>
+        <v>9350</v>
       </c>
       <c r="V10" s="7" t="n">
-        <v>1310</v>
+        <v>4212</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>20.2</v>
+        <v>83</v>
       </c>
       <c r="X10" s="2" t="n">
         <v>3</v>
@@ -1609,131 +1616,133 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t>09:55 breakdown: 5m low 22,472.15 breached OR-30L 22,508.40 | 10:00 retest: 5m high 22,527.40 tested OR-30L 22,508.40 as resistance | 10:05 confirmation: 5m close 22,506.15 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>10:00 breakdown: 5m low 24,267.30 breached OR-30L 24,272.55 | 10:05 retest: 5m high 24,276.55 tested OR-30L 24,272.55 as resistance | 11:00 confirmation: 5m close 24,242.90 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.33R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G11" s="11" t="n">
-        <v>22482.2</v>
+        <v>24179.3</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>22429.85</v>
+        <v>24209.4</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>22596.05</v>
+        <v>24089</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>52.35</v>
+        <v>30.1</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>22551.65</v>
+        <v>24194.05</v>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N11" s="11" t="n">
-        <v>69.45</v>
-      </c>
-      <c r="O11" s="12" t="n">
-        <v>1.33</v>
+        <v>-14.75</v>
+      </c>
+      <c r="O11" s="16" t="n">
+        <v>-0.49</v>
       </c>
       <c r="P11" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22600 CE</t>
+          <t>NIFTY 24100 PE</t>
         </is>
       </c>
       <c r="Q11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="R11" s="11" t="n">
-        <v>96.29000000000001</v>
+        <v>29.28</v>
       </c>
       <c r="S11" s="11" t="n">
-        <v>121.92</v>
+        <v>24.56</v>
       </c>
       <c r="T11" s="13" t="n">
-        <v>12518</v>
+        <v>5710</v>
       </c>
       <c r="U11" s="13" t="n">
-        <v>15850</v>
-      </c>
-      <c r="V11" s="14" t="n">
-        <v>3257</v>
-      </c>
-      <c r="W11" s="15" t="n">
-        <v>26</v>
+        <v>4789</v>
+      </c>
+      <c r="V11" s="17" t="n">
+        <v>-977</v>
+      </c>
+      <c r="W11" s="18" t="n">
+        <v>-17.1</v>
       </c>
       <c r="X11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z11" s="10" t="inlineStr">
         <is>
-          <t>09:50 breakout: 5m high 22,449.35 cleared OR-30H 22,433.25 | 09:55 retest: 5m low 22,434.85 tested OR-30H 22,433.25 as support | 10:10 confirmation: 5m close 22,482.20 held above OR-30H and VWAP</t>
-        </is>
-      </c>
+          <t>11:25 breakdown: 5m low 24,196.90 breached PDL 24,206.95 | 11:30 retest: 5m high 24,204.40 tested PDL 24,206.95 as resistance | 11:35 confirmation: 5m close 24,179.30 held below PDL and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA11" s="10" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1743,89 +1752,90 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>TARGET HIT (3R)</t>
+          <t>TRAILED (+0.36R)</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>22456.9</v>
+        <v>24138.1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>22503.1</v>
+        <v>24171.1</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>22318.3</v>
+        <v>24039.1</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>46.2</v>
+        <v>33</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>22318.3</v>
+        <v>24126.35</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>138.6</v>
+        <v>11.75</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>2.5</v>
+        <v>0.36</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22350 PE</t>
+          <t>NIFTY 24050 PE</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R12" s="4" t="n">
-        <v>100.98</v>
+        <v>115.9</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>163.09</v>
+        <v>120.5</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>13127</v>
+        <v>30134</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>21202</v>
+        <v>31330</v>
       </c>
       <c r="V12" s="7" t="n">
-        <v>7991</v>
+        <v>1091</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>60.9</v>
+        <v>3.6</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>09:50 breakdown: 5m low 22,445.70 breached OR-30L 22,459.95 | 09:55 retest: 5m high 22,483.00 tested OR-30L 22,459.95 as resistance | 10:25 confirmation: 5m close 22,456.90 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>09:20 breakdown: 5m low 24,129.15 breached PDL 24,144.45 | 09:50 retest: 5m high 24,166.10 tested PDL 24,144.45 as resistance | 09:55 confirmation: 5m close 24,138.10 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -1835,109 +1845,110 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>PDH Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+0.90R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G13" s="11" t="n">
-        <v>22504.1</v>
+        <v>24371.6</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>22555.65</v>
+        <v>24336.1</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>22349.45</v>
+        <v>24478.1</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>51.55</v>
+        <v>35.5</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>22457.5</v>
+        <v>24336.1</v>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="N13" s="11" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="O13" s="12" t="n">
-        <v>0.9</v>
+        <v>-35.5</v>
+      </c>
+      <c r="O13" s="16" t="n">
+        <v>-1</v>
       </c>
       <c r="P13" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22400 PE</t>
+          <t>NIFTY 24450 CE</t>
         </is>
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R13" s="11" t="n">
-        <v>102.9</v>
+        <v>105.33</v>
       </c>
       <c r="S13" s="11" t="n">
-        <v>121.28</v>
+        <v>91.06</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>13377</v>
+        <v>20539</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>15766</v>
-      </c>
-      <c r="V13" s="14" t="n">
-        <v>2314</v>
-      </c>
-      <c r="W13" s="15" t="n">
-        <v>17.3</v>
+        <v>17757</v>
+      </c>
+      <c r="V13" s="17" t="n">
+        <v>-2864</v>
+      </c>
+      <c r="W13" s="18" t="n">
+        <v>-13.9</v>
       </c>
       <c r="X13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z13" s="10" t="inlineStr">
         <is>
-          <t>09:20 breakdown: 5m low 22,521.70 breached PDL 22,546.55 | 09:25 retest: 5m high 22,550.65 tested PDL 22,546.55 as resistance | 09:30 confirmation: 5m close 22,504.10 held below PDL and VWAP</t>
-        </is>
-      </c>
+          <t>09:25 breakout: 5m high 24,355.85 cleared PDH 24,334.55 | 09:30 retest: 5m low 24,345.60 tested PDH 24,334.55 as support | 09:45 confirmation: 5m close 24,371.60 held above PDH and VWAP</t>
+        </is>
+      </c>
+      <c r="AA13" s="10" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 1 (General]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1947,99 +1958,100 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.42R)</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>22559.35</v>
+        <v>24303.1</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>22611.75</v>
+        <v>24337.65</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>22402.15</v>
+        <v>24147.62</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>52.4</v>
+        <v>34.55</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>22611.75</v>
+        <v>24288.45</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-52.4</v>
-      </c>
-      <c r="O14" s="16" t="n">
-        <v>-1</v>
+        <v>14.65</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>0.42</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22500 PE</t>
+          <t>NIFTY 24200 PE</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R14" s="4" t="n">
-        <v>129.62</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>107.95</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>16851</v>
+        <v>18301</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>14034</v>
-      </c>
-      <c r="V14" s="17" t="n">
-        <v>-2892</v>
-      </c>
-      <c r="W14" s="18" t="n">
-        <v>-17.2</v>
+        <v>19362</v>
+      </c>
+      <c r="V14" s="7" t="n">
+        <v>978</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>5.3</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t>13:15 breakdown: 5m low 22,552.60 breached PDL 22,561.80 | 13:25 retest: 5m high 22,585.45 tested PDL 22,561.80 as resistance | 14:15 confirmation: 5m close 22,559.35 held below PDL and VWAP</t>
-        </is>
-      </c>
+          <t>10:25 breakdown: 5m low 24,294.70 breached OR-30L 24,309.95 | 10:30 retest: 5m high 24,306.00 tested OR-30L 24,309.95 as resistance | 11:25 confirmation: 5m close 24,303.10 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 3 (Expensive]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -2049,89 +2061,90 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.23R)</t>
         </is>
       </c>
       <c r="G15" s="11" t="n">
-        <v>22575.8</v>
+        <v>24196.75</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>22611.75</v>
+        <v>24233.2</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>22467.95</v>
+        <v>24087.4</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>35.95</v>
+        <v>36.45</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>22611.75</v>
+        <v>24188.55</v>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N15" s="11" t="n">
-        <v>-35.95</v>
-      </c>
-      <c r="O15" s="23" t="n">
-        <v>-1</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O15" s="12" t="n">
+        <v>0.23</v>
       </c>
       <c r="P15" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22550 PE</t>
+          <t>NIFTY 24100 PE</t>
         </is>
       </c>
       <c r="Q15" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R15" s="11" t="n">
-        <v>145.36</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="S15" s="11" t="n">
-        <v>128.78</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="T15" s="13" t="n">
-        <v>18897</v>
+        <v>15516</v>
       </c>
       <c r="U15" s="13" t="n">
-        <v>16741</v>
-      </c>
-      <c r="V15" s="20" t="n">
-        <v>-2235</v>
-      </c>
-      <c r="W15" s="21" t="n">
-        <v>-11.8</v>
+        <v>16068</v>
+      </c>
+      <c r="V15" s="14" t="n">
+        <v>475</v>
+      </c>
+      <c r="W15" s="15" t="n">
+        <v>3.1</v>
       </c>
       <c r="X15" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y15" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z15" s="10" t="inlineStr">
         <is>
-          <t>10:05 breakdown: 5m low 22,578.35 breached OR-30L 22,585.40 | 13:15 retest: 5m high 22,585.90 tested OR-30L 22,585.40 as resistance | 13:55 confirmation: 5m close 22,575.80 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>09:30 breakdown: 5m low 24,198.40 breached PDL 24,207.75 | 09:35 retest: 5m high 24,211.70 tested PDL 24,207.75 as resistance | 10:00 confirmation: 5m close 24,196.75 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA15" s="10" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -2141,211 +2154,213 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.39R)</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>22658.15</v>
+        <v>24169.1</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>22618.45</v>
+        <v>24202.1</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>22777.25</v>
+        <v>24070.1</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>39.7</v>
+        <v>33</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>22618.45</v>
+        <v>24156.4</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 45m)</t>
         </is>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-39.7</v>
-      </c>
-      <c r="O16" s="16" t="n">
-        <v>-1</v>
+        <v>12.7</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>0.39</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22750 CE</t>
+          <t>NIFTY 24050 PE</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R16" s="4" t="n">
-        <v>146.03</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>129.6</v>
+        <v>75.06</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>37968</v>
+        <v>13837</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>33696</v>
-      </c>
-      <c r="V16" s="17" t="n">
-        <v>-4384</v>
-      </c>
-      <c r="W16" s="18" t="n">
-        <v>-11.5</v>
+        <v>14637</v>
+      </c>
+      <c r="V16" s="7" t="n">
+        <v>725</v>
+      </c>
+      <c r="W16" s="8" t="n">
+        <v>5.2</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>09:50 breakout: 5m high 22,637.70 cleared OR-30H 22,629.65 | 09:55 retest: 5m low 22,623.45 tested OR-30H 22,629.65 as support | 10:00 confirmation: 5m close 22,658.15 held above OR-30H and VWAP</t>
-        </is>
-      </c>
+          <t>10:05 breakdown: 5m low 24,181.55 breached OR-30L 24,188.80 | 10:10 retest: 5m high 24,196.45 tested OR-30L 24,188.80 as resistance | 10:45 confirmation: 5m close 24,169.10 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>PDH Support Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.07R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G17" s="11" t="n">
-        <v>22642.5</v>
+        <v>24083.15</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>22606.75</v>
+        <v>24114.65</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>22749.75</v>
+        <v>23988.65</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>35.75</v>
+        <v>31.5</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>22680.6</v>
+        <v>24101.4</v>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N17" s="11" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="O17" s="12" t="n">
-        <v>1.07</v>
+        <v>-18.25</v>
+      </c>
+      <c r="O17" s="16" t="n">
+        <v>-0.58</v>
       </c>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22750 CE</t>
+          <t>NIFTY 24000 PE</t>
         </is>
       </c>
       <c r="Q17" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R17" s="11" t="n">
-        <v>139.49</v>
+        <v>76.41</v>
       </c>
       <c r="S17" s="11" t="n">
-        <v>154.79</v>
+        <v>69.34</v>
       </c>
       <c r="T17" s="13" t="n">
-        <v>36267</v>
+        <v>14900</v>
       </c>
       <c r="U17" s="13" t="n">
-        <v>40245</v>
-      </c>
-      <c r="V17" s="14" t="n">
-        <v>3858</v>
-      </c>
-      <c r="W17" s="15" t="n">
-        <v>10.6</v>
+        <v>13521</v>
+      </c>
+      <c r="V17" s="17" t="n">
+        <v>-1452</v>
+      </c>
+      <c r="W17" s="18" t="n">
+        <v>-9.699999999999999</v>
       </c>
       <c r="X17" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y17" s="9" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z17" s="10" t="inlineStr">
         <is>
-          <t>09:45 breakout: 5m high 22,629.65 cleared PDH 22,621.80 | 09:50 retest: 5m low 22,611.75 tested PDH 22,621.80 as support | 09:55 confirmation: 5m close 22,642.50 held above PDH and VWAP</t>
-        </is>
-      </c>
+          <t>11:35 breakdown: 5m low 24,102.95 breached OR-30L 24,107.10 | 11:40 retest: 5m high 24,108.95 tested OR-30L 24,107.10 as resistance | 12:00 confirmation: 5m close 24,083.15 held below OR-30L and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA17" s="10" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 1 (General]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2355,89 +2370,90 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>TARGET HIT (3R)</t>
+          <t>TRAILED (+0.22R)</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>22485.7</v>
+        <v>24043.05</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>22534.3</v>
+        <v>24090.1</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>22339.9</v>
+        <v>23901.9</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>48.6</v>
+        <v>47.05</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>22339.9</v>
+        <v>24032.7</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N18" s="4" t="n">
-        <v>145.8</v>
+        <v>10.35</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>2.5</v>
+        <v>0.22</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 22450 PE</t>
+          <t>NIFTY 23950 PE</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R18" s="4" t="n">
-        <v>126.18</v>
+        <v>24.47</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>204.29</v>
+        <v>26.84</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>16403</v>
+        <v>4772</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>26558</v>
+        <v>5234</v>
       </c>
       <c r="V18" s="7" t="n">
-        <v>10062</v>
+        <v>405</v>
       </c>
       <c r="W18" s="8" t="n">
-        <v>61.3</v>
+        <v>8.5</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>12:15 breakdown: 5m low 22,500.80 breached OR-30L 22,508.35 | 12:20 retest: 5m high 22,529.30 tested OR-30L 22,508.35 as resistance | 12:25 confirmation: 5m close 22,485.70 held below OR-30L and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
-        </is>
-      </c>
+          <t>09:20 breakdown: 5m low 24,040.20 breached PDL 24,077.00 | 09:25 retest: 5m high 24,085.10 tested PDL 24,077.00 as resistance | 09:30 confirmation: 5m close 24,043.05 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -2447,7 +2463,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -2457,89 +2473,90 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.03R)</t>
+          <t>TRAILED (+0.35R)</t>
         </is>
       </c>
       <c r="G19" s="11" t="n">
-        <v>22838.25</v>
+        <v>24017.85</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>22876.75</v>
+        <v>24048.35</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>22722.75</v>
+        <v>23926.35</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>38.5</v>
+        <v>30.5</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>22798.55</v>
+        <v>24007.05</v>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N19" s="11" t="n">
-        <v>39.7</v>
+        <v>10.8</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>1.03</v>
+        <v>0.35</v>
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 22750 PE</t>
+          <t>NIFTY 23900 PE</t>
         </is>
       </c>
       <c r="Q19" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="R19" s="11" t="n">
-        <v>29.08</v>
+        <v>17.87</v>
       </c>
       <c r="S19" s="11" t="n">
-        <v>37.52</v>
+        <v>19.82</v>
       </c>
       <c r="T19" s="13" t="n">
-        <v>5671</v>
+        <v>4646</v>
       </c>
       <c r="U19" s="13" t="n">
-        <v>7316</v>
+        <v>5153</v>
       </c>
       <c r="V19" s="14" t="n">
-        <v>1586</v>
+        <v>450</v>
       </c>
       <c r="W19" s="15" t="n">
-        <v>28</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X19" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y19" s="9" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="Z19" s="10" t="inlineStr">
         <is>
-          <t>10:10 breakdown: 5m low 22,850.60 breached OR-30L 22,855.45 | 10:15 retest: 5m high 22,871.75 tested OR-30L 22,855.45 as resistance | 10:25 confirmation: 5m close 22,838.25 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>09:50 breakdown: 5m low 24,019.65 breached OR-30L 24,024.40 | 09:55 retest: 5m high 24,036.15 tested OR-30L 24,024.40 as resistance | 10:15 confirmation: 5m close 24,017.85 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA19" s="10" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2549,7 +2566,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip [Tier 1 (General]</t>
+          <t>OR-30H Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2559,99 +2576,100 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>23440.4</v>
+        <v>24107.05</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>23407.5</v>
+        <v>24067.4</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>23539.1</v>
+        <v>24226</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>32.9</v>
+        <v>39.65</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>23417.75</v>
+        <v>24110.6</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-22.65</v>
-      </c>
-      <c r="O20" s="16" t="n">
-        <v>-0.6899999999999999</v>
+        <v>3.55</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0.09</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23500 CE</t>
+          <t>NIFTY 24200 CE</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R20" s="4" t="n">
-        <v>106.14</v>
+        <v>109.25</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>95.06999999999999</v>
+        <v>110.45</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>13798</v>
+        <v>28405</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>12359</v>
-      </c>
-      <c r="V20" s="17" t="n">
-        <v>-1510</v>
-      </c>
-      <c r="W20" s="18" t="n">
-        <v>-10.9</v>
+        <v>28717</v>
+      </c>
+      <c r="V20" s="7" t="n">
+        <v>212</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>0.7</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y20" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t>10:50 breakout: 5m high 23,421.30 cleared OR-30H 23,413.90 | 10:55 retest: 5m low 23,413.45 tested OR-30H 23,413.90 as support | 11:35 confirmation: 5m close 23,440.40 held above OR-30H and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
-        </is>
-      </c>
+          <t>10:55 breakout: 5m high 24,092.45 cleared OR-30H 24,077.05 | 11:00 retest: 5m low 24,074.45 tested OR-30H 24,077.05 as support | 11:15 confirmation: 5m close 24,107.05 held above OR-30H and VWAP</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -2661,104 +2679,105 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.80R)</t>
+          <t>TRAILED (+0.34R)</t>
         </is>
       </c>
       <c r="G21" s="11" t="n">
-        <v>23383.3</v>
+        <v>23978.55</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>23427.25</v>
+        <v>24015.95</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>23251.45</v>
+        <v>23866.35</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>43.95</v>
+        <v>37.4</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>23312.85</v>
+        <v>23966</v>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>Partial + Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N21" s="11" t="n">
-        <v>70.45</v>
+        <v>12.55</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>1.8</v>
+        <v>0.34</v>
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23300 PE</t>
+          <t>NIFTY 23900 PE</t>
         </is>
       </c>
       <c r="Q21" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R21" s="11" t="n">
-        <v>109.2</v>
+        <v>112.63</v>
       </c>
       <c r="S21" s="11" t="n">
-        <v>139.1</v>
+        <v>117.65</v>
       </c>
       <c r="T21" s="13" t="n">
-        <v>28392</v>
+        <v>21963</v>
       </c>
       <c r="U21" s="13" t="n">
-        <v>36166</v>
+        <v>22942</v>
       </c>
       <c r="V21" s="14" t="n">
-        <v>7663</v>
+        <v>889</v>
       </c>
       <c r="W21" s="15" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="X21" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y21" s="9" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z21" s="10" t="inlineStr">
         <is>
-          <t>10:35 breakdown: 5m low 23,414.25 breached OR-30L 23,425.80 | 10:40 retest: 5m high 23,422.25 tested OR-30L 23,425.80 as resistance | 10:45 confirmation: 5m close 23,383.30 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>13:55 breakdown: 5m low 23,988.20 breached PDL 23,993.85 | 14:00 retest: 5m high 24,010.95 tested PDL 23,993.85 as resistance | 14:05 confirmation: 5m close 23,978.55 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA21" s="10" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>PDH Support Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2767,165 +2786,166 @@
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>23400.25</v>
+        <v>23929.5</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>23367.7</v>
+        <v>23981.05</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>23497.9</v>
+        <v>23791.05</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>32.55</v>
+        <v>51.55</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>23367.7</v>
+        <v>23965.05</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-32.55</v>
-      </c>
-      <c r="O22" s="16" t="n">
-        <v>-1</v>
+        <v>-35.55</v>
+      </c>
+      <c r="O22" s="19" t="n">
+        <v>-0.6899999999999999</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23500 CE</t>
+          <t>NIFTY 23850 PE</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R22" s="4" t="n">
-        <v>24.77</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>16.54</v>
+        <v>81.8</v>
       </c>
       <c r="T22" s="6" t="n">
-        <v>6440</v>
+        <v>18652</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>4300</v>
-      </c>
-      <c r="V22" s="17" t="n">
-        <v>-2196</v>
-      </c>
-      <c r="W22" s="18" t="n">
-        <v>-34.1</v>
+        <v>15951</v>
+      </c>
+      <c r="V22" s="20" t="n">
+        <v>-2779</v>
+      </c>
+      <c r="W22" s="21" t="n">
+        <v>-14.9</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t>09:20 breakout: 5m high 23,396.35 cleared PDH 23,389.15 | 09:25 retest: 5m low 23,372.70 tested PDH 23,389.15 as support | 09:30 confirmation: 5m close 23,400.25 held above PDH and VWAP</t>
-        </is>
-      </c>
+          <t>10:45 breakdown: 5m low 23,952.60 breached OR-30L 23,955.40 | 10:50 retest: 5m high 23,976.05 tested OR-30L 23,955.40 as resistance | 11:10 confirmation: 5m close 23,929.50 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 1 (General]</t>
+          <t>OR-30H Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+0.95R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G23" s="11" t="n">
-        <v>23202.8</v>
+        <v>23963.8</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>23234.3</v>
+        <v>23931.05</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>23108.3</v>
+        <v>24019.85</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>31.5</v>
+        <v>32.75</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>23172.95</v>
+        <v>23965.35</v>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N23" s="11" t="n">
-        <v>29.85</v>
+        <v>1.55</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>0.95</v>
+        <v>0.05</v>
       </c>
       <c r="P23" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23150 PE</t>
+          <t>NIFTY 24050 CE</t>
         </is>
       </c>
       <c r="Q23" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R23" s="11" t="n">
-        <v>132.84</v>
+        <v>78.55</v>
       </c>
       <c r="S23" s="11" t="n">
-        <v>146.21</v>
+        <v>78.83</v>
       </c>
       <c r="T23" s="13" t="n">
-        <v>25904</v>
+        <v>15317</v>
       </c>
       <c r="U23" s="13" t="n">
-        <v>28511</v>
-      </c>
-      <c r="V23" s="14" t="n">
-        <v>2508</v>
-      </c>
-      <c r="W23" s="15" t="n">
-        <v>9.699999999999999</v>
+        <v>15372</v>
+      </c>
+      <c r="V23" s="17" t="n">
+        <v>-21</v>
+      </c>
+      <c r="W23" s="18" t="n">
+        <v>-0.1</v>
       </c>
       <c r="X23" s="9" t="n">
         <v>3</v>
@@ -2935,19 +2955,20 @@
       </c>
       <c r="Z23" s="10" t="inlineStr">
         <is>
-          <t>14:15 breakdown: 5m low 23,229.40 breached PDL 23,232.25 | 14:20 retest: 5m high 23,229.30 tested PDL 23,232.25 as resistance | 14:30 confirmation: 5m close 23,202.80 held below PDL and VWAP</t>
-        </is>
-      </c>
+          <t>10:00 breakout: 5m high 23,954.90 cleared OR-30H 23,948.35 | 10:05 retest: 5m low 23,947.15 tested OR-30H 23,948.35 as support | 10:30 confirmation: 5m close 23,963.80 held above OR-30H and VWAP</t>
+        </is>
+      </c>
+      <c r="AA23" s="10" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2957,7 +2978,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2967,67 +2988,67 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+0.92R)</t>
+          <t>TRAILED (+0.21R)</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>23394.6</v>
+        <v>23796.55</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>23431.6</v>
+        <v>23832.8</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>23235.25</v>
+        <v>23687.8</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>37</v>
+        <v>36.25</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>23360.45</v>
+        <v>23789</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N24" s="4" t="n">
-        <v>34.15</v>
+        <v>7.55</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>0.92</v>
+        <v>0.21</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23300 PE</t>
+          <t>NIFTY 23700 PE</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="R24" s="4" t="n">
-        <v>118.2</v>
+        <v>22.37</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>132.06</v>
+        <v>23.87</v>
       </c>
       <c r="T24" s="6" t="n">
-        <v>30732</v>
+        <v>5816</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>34336</v>
+        <v>6206</v>
       </c>
       <c r="V24" s="7" t="n">
-        <v>3494</v>
+        <v>331</v>
       </c>
       <c r="W24" s="8" t="n">
-        <v>11.4</v>
+        <v>5.7</v>
       </c>
       <c r="X24" s="2" t="n">
         <v>4</v>
@@ -3037,19 +3058,20 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>09:50 breakdown: 5m low 23,415.55 breached OR-30L 23,439.35 | 09:55 retest: 5m high 23,426.60 tested OR-30L 23,439.35 as resistance | 10:00 confirmation: 5m close 23,394.60 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>09:55 breakdown: 5m low 23,815.00 breached OR-30L 23,819.15 | 10:00 retest: 5m high 23,827.80 tested OR-30L 23,819.15 as resistance | 10:20 confirmation: 5m close 23,796.55 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -3059,53 +3081,53 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.36R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G25" s="11" t="n">
-        <v>23297.2</v>
+        <v>23669.3</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>23264.6</v>
+        <v>23722.25</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>23377.65</v>
+        <v>23510.45</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>32.6</v>
+        <v>52.95</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>23341.5</v>
+        <v>23684.35</v>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N25" s="11" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="O25" s="12" t="n">
-        <v>1.36</v>
+        <v>-15.05</v>
+      </c>
+      <c r="O25" s="16" t="n">
+        <v>-0.28</v>
       </c>
       <c r="P25" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23400 CE</t>
+          <t>NIFTY 23550 PE</t>
         </is>
       </c>
       <c r="Q25" s="9" t="inlineStr">
@@ -3114,39 +3136,40 @@
         </is>
       </c>
       <c r="R25" s="11" t="n">
-        <v>73.81</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="S25" s="11" t="n">
-        <v>90.41</v>
+        <v>89.87</v>
       </c>
       <c r="T25" s="13" t="n">
-        <v>14393</v>
+        <v>24848</v>
       </c>
       <c r="U25" s="13" t="n">
-        <v>17630</v>
-      </c>
-      <c r="V25" s="14" t="n">
-        <v>3158</v>
-      </c>
-      <c r="W25" s="15" t="n">
-        <v>21.9</v>
+        <v>23366</v>
+      </c>
+      <c r="V25" s="17" t="n">
+        <v>-1573</v>
+      </c>
+      <c r="W25" s="18" t="n">
+        <v>-6.3</v>
       </c>
       <c r="X25" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y25" s="9" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="Z25" s="10" t="inlineStr">
         <is>
-          <t>10:05 breakout: 5m high 23,274.80 cleared OR-30H 23,270.90 | 10:10 retest: 5m low 23,269.60 tested OR-30H 23,270.90 as support | 10:15 confirmation: 5m close 23,297.20 held above OR-30H and VWAP</t>
-        </is>
-      </c>
+          <t>10:00 breakdown: 5m low 23,664.85 breached OR-30L 23,669.65 | 10:05 retest: 5m high 23,674.85 tested OR-30L 23,669.65 as resistance | 10:45 confirmation: 5m close 23,669.30 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA25" s="10" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -3161,12 +3184,12 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30H Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3175,39 +3198,39 @@
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>23409.75</v>
+        <v>23535.6</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>23456.35</v>
+        <v>23496.6</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>23269.95</v>
+        <v>23620.25</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>46.6</v>
+        <v>39</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>23456.35</v>
+        <v>23515.45</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-46.6</v>
-      </c>
-      <c r="O26" s="16" t="n">
-        <v>-1</v>
+        <v>-20.15</v>
+      </c>
+      <c r="O26" s="19" t="n">
+        <v>-0.52</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23300 PE</t>
+          <t>NIFTY 23650 CE</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3216,34 +3239,35 @@
         </is>
       </c>
       <c r="R26" s="4" t="n">
-        <v>84.7</v>
+        <v>87.92</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>68.17</v>
+        <v>80.38</v>
       </c>
       <c r="T26" s="6" t="n">
-        <v>11011</v>
+        <v>17144</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>8862</v>
-      </c>
-      <c r="V26" s="17" t="n">
-        <v>-2214</v>
-      </c>
-      <c r="W26" s="18" t="n">
-        <v>-20.1</v>
+        <v>15674</v>
+      </c>
+      <c r="V26" s="20" t="n">
+        <v>-1547</v>
+      </c>
+      <c r="W26" s="21" t="n">
+        <v>-9</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>10:10 breakdown: 5m low 23,404.50 breached OR-30L 23,410.15 | 10:15 retest: 5m high 23,417.00 tested OR-30L 23,410.15 as resistance | 11:00 confirmation: 5m close 23,409.75 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>10:25 breakout: 5m high 23,549.00 cleared OR-30H 23,533.45 | 10:30 retest: 5m low 23,533.10 tested OR-30H 23,533.45 as support | 11:00 confirmation: 5m close 23,535.60 held above OR-30H and VWAP</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
@@ -3263,7 +3287,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -3304,7 +3328,7 @@
       <c r="N27" s="11" t="n">
         <v>-32.9</v>
       </c>
-      <c r="O27" s="23" t="n">
+      <c r="O27" s="16" t="n">
         <v>-1</v>
       </c>
       <c r="P27" s="10" t="inlineStr">
@@ -3329,10 +3353,10 @@
       <c r="U27" s="13" t="n">
         <v>13820</v>
       </c>
-      <c r="V27" s="20" t="n">
+      <c r="V27" s="17" t="n">
         <v>-2281</v>
       </c>
-      <c r="W27" s="21" t="n">
+      <c r="W27" s="18" t="n">
         <v>-14.2</v>
       </c>
       <c r="X27" s="9" t="n">
@@ -3346,11 +3370,12 @@
           <t>09:25 breakdown: 5m low 23,414.40 breached PDL 23,431.50 | 09:30 retest: 5m high 23,446.40 tested PDL 23,431.50 as resistance | 09:40 confirmation: 5m close 23,418.50 held below PDL and VWAP</t>
         </is>
       </c>
+      <c r="AA27" s="10" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -3365,12 +3390,12 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3379,39 +3404,39 @@
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>23535.6</v>
+        <v>23409.75</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>23496.6</v>
+        <v>23456.35</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>23620.25</v>
+        <v>23269.95</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>39</v>
+        <v>46.6</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>23496.6</v>
+        <v>23420.45</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-39</v>
-      </c>
-      <c r="O28" s="16" t="n">
-        <v>-1</v>
+        <v>-10.7</v>
+      </c>
+      <c r="O28" s="19" t="n">
+        <v>-0.23</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23650 CE</t>
+          <t>NIFTY 23300 PE</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3420,44 +3445,45 @@
         </is>
       </c>
       <c r="R28" s="4" t="n">
-        <v>87.92</v>
+        <v>84.7</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>73.78</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="T28" s="6" t="n">
-        <v>11430</v>
+        <v>16516</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>9591</v>
-      </c>
-      <c r="V28" s="17" t="n">
-        <v>-1904</v>
-      </c>
-      <c r="W28" s="18" t="n">
-        <v>-16.7</v>
+        <v>15705</v>
+      </c>
+      <c r="V28" s="20" t="n">
+        <v>-888</v>
+      </c>
+      <c r="W28" s="21" t="n">
+        <v>-5.4</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y28" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>10:25 breakout: 5m high 23,549.00 cleared OR-30H 23,533.45 | 10:30 retest: 5m low 23,533.10 tested OR-30H 23,533.45 as support | 11:00 confirmation: 5m close 23,535.60 held above OR-30H and VWAP</t>
-        </is>
-      </c>
+          <t>10:10 breakdown: 5m low 23,404.50 breached OR-30L 23,410.15 | 10:15 retest: 5m high 23,417.00 tested OR-30L 23,410.15 as resistance | 11:00 confirmation: 5m close 23,409.75 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -3467,53 +3493,53 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30H Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+0.41R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G29" s="11" t="n">
-        <v>23669.3</v>
+        <v>23297.2</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>23722.25</v>
+        <v>23264.6</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>23510.45</v>
+        <v>23377.65</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>52.95</v>
+        <v>32.6</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>23647.3</v>
+        <v>23296.65</v>
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N29" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="O29" s="12" t="n">
-        <v>0.41</v>
+        <v>-0.55</v>
+      </c>
+      <c r="O29" s="16" t="n">
+        <v>-0.02</v>
       </c>
       <c r="P29" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23550 PE</t>
+          <t>NIFTY 23400 CE</t>
         </is>
       </c>
       <c r="Q29" s="9" t="inlineStr">
@@ -3522,44 +3548,45 @@
         </is>
       </c>
       <c r="R29" s="11" t="n">
-        <v>95.56999999999999</v>
+        <v>73.81</v>
       </c>
       <c r="S29" s="11" t="n">
-        <v>102.14</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="T29" s="13" t="n">
-        <v>24848</v>
+        <v>14393</v>
       </c>
       <c r="U29" s="13" t="n">
-        <v>26556</v>
-      </c>
-      <c r="V29" s="14" t="n">
-        <v>1612</v>
-      </c>
-      <c r="W29" s="15" t="n">
-        <v>6.5</v>
+        <v>14292</v>
+      </c>
+      <c r="V29" s="17" t="n">
+        <v>-175</v>
+      </c>
+      <c r="W29" s="18" t="n">
+        <v>-1.2</v>
       </c>
       <c r="X29" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y29" s="9" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z29" s="10" t="inlineStr">
         <is>
-          <t>10:00 breakdown: 5m low 23,664.85 breached OR-30L 23,669.65 | 10:05 retest: 5m high 23,674.85 tested OR-30L 23,669.65 as resistance | 10:45 confirmation: 5m close 23,669.30 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>10:05 breakout: 5m high 23,274.80 cleared OR-30H 23,270.90 | 10:10 retest: 5m low 23,269.60 tested OR-30H 23,270.90 as support | 10:15 confirmation: 5m close 23,297.20 held above OR-30H and VWAP</t>
+        </is>
+      </c>
+      <c r="AA29" s="10" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3569,7 +3596,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3579,27 +3606,27 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+1.25R)</t>
+          <t>TRAILED (+0.92R)</t>
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>23796.55</v>
+        <v>23394.6</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>23832.8</v>
+        <v>23431.6</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>23687.8</v>
+        <v>23235.25</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>36.25</v>
+        <v>37</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>23751.4</v>
+        <v>23360.45</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -3608,38 +3635,38 @@
         </is>
       </c>
       <c r="N30" s="4" t="n">
-        <v>45.15</v>
+        <v>34.15</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>1.25</v>
+        <v>0.92</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23700 PE</t>
+          <t>NIFTY 23300 PE</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="R30" s="4" t="n">
-        <v>22.37</v>
+        <v>118.2</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>33.47</v>
+        <v>132.06</v>
       </c>
       <c r="T30" s="6" t="n">
-        <v>5816</v>
+        <v>30732</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>8702</v>
+        <v>34336</v>
       </c>
       <c r="V30" s="7" t="n">
-        <v>2824</v>
+        <v>3494</v>
       </c>
       <c r="W30" s="8" t="n">
-        <v>48.6</v>
+        <v>11.4</v>
       </c>
       <c r="X30" s="2" t="n">
         <v>4</v>
@@ -3649,233 +3676,236 @@
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t>09:55 breakdown: 5m low 23,815.00 breached OR-30L 23,819.15 | 10:00 retest: 5m high 23,827.80 tested OR-30L 23,819.15 as resistance | 10:20 confirmation: 5m close 23,796.55 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>09:50 breakdown: 5m low 23,415.55 breached OR-30L 23,439.35 | 09:55 retest: 5m high 23,426.60 tested OR-30L 23,439.35 as resistance | 10:00 confirmation: 5m close 23,394.60 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>TRAILED (+0.95R)</t>
         </is>
       </c>
       <c r="G31" s="11" t="n">
-        <v>23963.8</v>
+        <v>23202.8</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>23931.05</v>
+        <v>23234.3</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>24019.85</v>
+        <v>23108.3</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>32.75</v>
+        <v>31.5</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>23963.8</v>
+        <v>23172.95</v>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
-          <t>Breakeven</t>
+          <t>Time (15:10)</t>
         </is>
       </c>
       <c r="N31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="19" t="n">
-        <v>0</v>
+        <v>29.85</v>
+      </c>
+      <c r="O31" s="12" t="n">
+        <v>0.95</v>
       </c>
       <c r="P31" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24050 CE</t>
+          <t>NIFTY 23100 PE</t>
         </is>
       </c>
       <c r="Q31" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="R31" s="11" t="n">
-        <v>78.55</v>
+        <v>111.57</v>
       </c>
       <c r="S31" s="11" t="n">
-        <v>77.67</v>
+        <v>123.46</v>
       </c>
       <c r="T31" s="13" t="n">
-        <v>10212</v>
+        <v>21756</v>
       </c>
       <c r="U31" s="13" t="n">
-        <v>10097</v>
-      </c>
-      <c r="V31" s="20" t="n">
-        <v>-180</v>
-      </c>
-      <c r="W31" s="21" t="n">
-        <v>-1.8</v>
+        <v>24075</v>
+      </c>
+      <c r="V31" s="14" t="n">
+        <v>2228</v>
+      </c>
+      <c r="W31" s="15" t="n">
+        <v>10.2</v>
       </c>
       <c r="X31" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y31" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z31" s="10" t="inlineStr">
         <is>
-          <t>10:00 breakout: 5m high 23,954.90 cleared OR-30H 23,948.35 | 10:05 retest: 5m low 23,947.15 tested OR-30H 23,948.35 as support | 10:30 confirmation: 5m close 23,963.80 held above OR-30H and VWAP</t>
-        </is>
-      </c>
+          <t>14:15 breakdown: 5m low 23,229.40 breached PDL 23,232.25 | 14:20 retest: 5m high 23,229.30 tested PDL 23,232.25 as resistance | 14:30 confirmation: 5m close 23,202.80 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA31" s="10" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>PDH Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+0.81R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>23929.5</v>
+        <v>23400.25</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>23981.05</v>
+        <v>23367.7</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>23791.05</v>
+        <v>23497.9</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>51.55</v>
+        <v>32.55</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>23887.95</v>
+        <v>23382.9</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N32" s="4" t="n">
-        <v>41.55</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>-17.35</v>
+      </c>
+      <c r="O32" s="19" t="n">
+        <v>-0.53</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23850 PE</t>
+          <t>NIFTY 23500 CE</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="R32" s="4" t="n">
-        <v>95.65000000000001</v>
+        <v>24.77</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>111.26</v>
+        <v>20.06</v>
       </c>
       <c r="T32" s="6" t="n">
-        <v>12434</v>
+        <v>6440</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>14464</v>
-      </c>
-      <c r="V32" s="7" t="n">
-        <v>1956</v>
-      </c>
-      <c r="W32" s="8" t="n">
-        <v>15.7</v>
+        <v>5216</v>
+      </c>
+      <c r="V32" s="20" t="n">
+        <v>-1282</v>
+      </c>
+      <c r="W32" s="21" t="n">
+        <v>-19.9</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y32" s="2" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>10:45 breakdown: 5m low 23,952.60 breached OR-30L 23,955.40 | 10:50 retest: 5m high 23,976.05 tested OR-30L 23,955.40 as resistance | 11:10 confirmation: 5m close 23,929.50 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>09:20 breakout: 5m high 23,396.35 cleared PDH 23,389.15 | 09:25 retest: 5m low 23,372.70 tested PDH 23,389.15 as support | 09:30 confirmation: 5m close 23,400.25 held above PDH and VWAP</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 1 (General]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -3885,89 +3915,90 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+0.24R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G33" s="11" t="n">
-        <v>23978.55</v>
+        <v>23383.3</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>24015.95</v>
+        <v>23427.25</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>23866.35</v>
+        <v>23251.45</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>37.4</v>
+        <v>43.95</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>23969.65</v>
+        <v>23385.3</v>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N33" s="11" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="O33" s="12" t="n">
-        <v>0.24</v>
+        <v>-2</v>
+      </c>
+      <c r="O33" s="16" t="n">
+        <v>-0.05</v>
       </c>
       <c r="P33" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23950 PE</t>
+          <t>NIFTY 23300 PE</t>
         </is>
       </c>
       <c r="Q33" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="R33" s="11" t="n">
-        <v>134.93</v>
+        <v>109.2</v>
       </c>
       <c r="S33" s="11" t="n">
-        <v>138.65</v>
+        <v>108.14</v>
       </c>
       <c r="T33" s="13" t="n">
-        <v>26311</v>
+        <v>28392</v>
       </c>
       <c r="U33" s="13" t="n">
-        <v>27037</v>
-      </c>
-      <c r="V33" s="14" t="n">
-        <v>628</v>
-      </c>
-      <c r="W33" s="15" t="n">
-        <v>2.4</v>
+        <v>28116</v>
+      </c>
+      <c r="V33" s="17" t="n">
+        <v>-375</v>
+      </c>
+      <c r="W33" s="18" t="n">
+        <v>-1.3</v>
       </c>
       <c r="X33" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y33" s="9" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="Z33" s="10" t="inlineStr">
         <is>
-          <t>13:55 breakdown: 5m low 23,988.20 breached PDL 23,993.85 | 14:00 retest: 5m high 24,010.95 tested PDL 23,993.85 as resistance | 14:05 confirmation: 5m close 23,978.55 held below PDL and VWAP</t>
-        </is>
-      </c>
+          <t>10:35 breakdown: 5m low 23,414.25 breached OR-30L 23,425.80 | 10:40 retest: 5m high 23,422.25 tested OR-30L 23,425.80 as resistance | 10:45 confirmation: 5m close 23,383.30 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA33" s="10" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -3977,7 +4008,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>OR-30H Support Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30H Support Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3987,89 +4018,90 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.24R)</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>24107.05</v>
+        <v>23440.4</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>24067.4</v>
+        <v>23407.5</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>24226</v>
+        <v>23539.1</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>39.65</v>
+        <v>32.9</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>24067.4</v>
+        <v>23448.4</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-39.65</v>
-      </c>
-      <c r="O34" s="16" t="n">
-        <v>-1</v>
+        <v>8</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0.24</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24200 CE</t>
+          <t>NIFTY 23550 CE</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="R34" s="4" t="n">
-        <v>109.25</v>
+        <v>86.25</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>93.11</v>
+        <v>89.03</v>
       </c>
       <c r="T34" s="6" t="n">
-        <v>28405</v>
+        <v>16819</v>
       </c>
       <c r="U34" s="6" t="n">
-        <v>24209</v>
-      </c>
-      <c r="V34" s="17" t="n">
-        <v>-4290</v>
-      </c>
-      <c r="W34" s="18" t="n">
-        <v>-15.1</v>
+        <v>17361</v>
+      </c>
+      <c r="V34" s="7" t="n">
+        <v>463</v>
+      </c>
+      <c r="W34" s="8" t="n">
+        <v>2.8</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>10:55 breakout: 5m high 24,092.45 cleared OR-30H 24,077.05 | 11:00 retest: 5m low 24,074.45 tested OR-30H 24,077.05 as support | 11:15 confirmation: 5m close 24,107.05 held above OR-30H and VWAP</t>
-        </is>
-      </c>
+          <t>10:50 breakout: 5m high 23,421.30 cleared OR-30H 23,413.90 | 10:55 retest: 5m low 23,413.45 tested OR-30H 23,413.90 as support | 11:35 confirmation: 5m close 23,440.40 held above OR-30H and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
@@ -4079,7 +4111,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -4093,95 +4125,96 @@
         </is>
       </c>
       <c r="G35" s="11" t="n">
-        <v>24017.85</v>
+        <v>22838.25</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>24048.35</v>
+        <v>22876.75</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>23926.35</v>
+        <v>22722.75</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>30.5</v>
+        <v>38.5</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>24048.35</v>
+        <v>22838.9</v>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N35" s="11" t="n">
-        <v>-30.5</v>
-      </c>
-      <c r="O35" s="23" t="n">
-        <v>-1</v>
+        <v>-0.65</v>
+      </c>
+      <c r="O35" s="16" t="n">
+        <v>-0.02</v>
       </c>
       <c r="P35" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23900 PE</t>
+          <t>NIFTY 22750 PE</t>
         </is>
       </c>
       <c r="Q35" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="R35" s="11" t="n">
-        <v>17.87</v>
+        <v>29.08</v>
       </c>
       <c r="S35" s="11" t="n">
-        <v>11.25</v>
+        <v>28.34</v>
       </c>
       <c r="T35" s="13" t="n">
-        <v>4646</v>
+        <v>5671</v>
       </c>
       <c r="U35" s="13" t="n">
-        <v>2925</v>
-      </c>
-      <c r="V35" s="20" t="n">
-        <v>-1775</v>
-      </c>
-      <c r="W35" s="21" t="n">
-        <v>-38.2</v>
+        <v>5526</v>
+      </c>
+      <c r="V35" s="17" t="n">
+        <v>-202</v>
+      </c>
+      <c r="W35" s="18" t="n">
+        <v>-3.6</v>
       </c>
       <c r="X35" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y35" s="9" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z35" s="10" t="inlineStr">
         <is>
-          <t>09:50 breakdown: 5m low 24,019.65 breached OR-30L 24,024.40 | 09:55 retest: 5m high 24,036.15 tested OR-30L 24,024.40 as resistance | 10:15 confirmation: 5m close 24,017.85 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>10:10 breakdown: 5m low 22,850.60 breached OR-30L 22,855.45 | 10:15 retest: 5m high 22,871.75 tested OR-30L 22,855.45 as resistance | 10:25 confirmation: 5m close 22,838.25 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA35" s="10" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4191,67 +4224,67 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>TARGET HIT (3R)</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>24043.05</v>
+        <v>22485.7</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>24090.1</v>
+        <v>22534.3</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>23901.9</v>
+        <v>22339.9</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>47.05</v>
+        <v>48.6</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>24043.05</v>
+        <v>22339.9</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>Breakeven</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="22" t="n">
-        <v>-0</v>
+        <v>145.8</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 23950 PE</t>
+          <t>NIFTY 22400 PE</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="R36" s="4" t="n">
-        <v>24.47</v>
+        <v>104.38</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>22.45</v>
+        <v>174.43</v>
       </c>
       <c r="T36" s="6" t="n">
-        <v>4772</v>
+        <v>20354</v>
       </c>
       <c r="U36" s="6" t="n">
-        <v>4378</v>
-      </c>
-      <c r="V36" s="17" t="n">
-        <v>-449</v>
-      </c>
-      <c r="W36" s="18" t="n">
-        <v>-9.4</v>
+        <v>34014</v>
+      </c>
+      <c r="V36" s="7" t="n">
+        <v>13555</v>
+      </c>
+      <c r="W36" s="8" t="n">
+        <v>66.59999999999999</v>
       </c>
       <c r="X36" s="2" t="n">
         <v>3</v>
@@ -4261,121 +4294,123 @@
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>09:20 breakdown: 5m low 24,040.20 breached PDL 24,077.00 | 09:25 retest: 5m high 24,085.10 tested PDL 24,077.00 as resistance | 09:30 confirmation: 5m close 24,043.05 held below PDL and VWAP</t>
-        </is>
-      </c>
+          <t>12:15 breakdown: 5m low 22,500.80 breached OR-30L 22,508.35 | 12:20 retest: 5m high 22,529.30 tested OR-30L 22,508.35 as resistance | 12:25 confirmation: 5m close 22,485.70 held below OR-30L and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 1 (General]</t>
+          <t>PDH Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.22R)</t>
         </is>
       </c>
       <c r="G37" s="11" t="n">
-        <v>24083.15</v>
+        <v>22642.5</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>24114.65</v>
+        <v>22606.75</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>23988.65</v>
+        <v>22749.75</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>31.5</v>
+        <v>35.75</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>24114.65</v>
+        <v>22650.35</v>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N37" s="11" t="n">
-        <v>-31.5</v>
-      </c>
-      <c r="O37" s="23" t="n">
-        <v>-1</v>
+        <v>7.85</v>
+      </c>
+      <c r="O37" s="12" t="n">
+        <v>0.22</v>
       </c>
       <c r="P37" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24050 PE</t>
+          <t>NIFTY 22750 CE</t>
         </is>
       </c>
       <c r="Q37" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R37" s="11" t="n">
-        <v>97.47</v>
+        <v>139.49</v>
       </c>
       <c r="S37" s="11" t="n">
-        <v>83.11</v>
+        <v>142.46</v>
       </c>
       <c r="T37" s="13" t="n">
-        <v>12671</v>
+        <v>36267</v>
       </c>
       <c r="U37" s="13" t="n">
-        <v>10804</v>
-      </c>
-      <c r="V37" s="20" t="n">
-        <v>-1935</v>
-      </c>
-      <c r="W37" s="21" t="n">
-        <v>-15.3</v>
+        <v>37040</v>
+      </c>
+      <c r="V37" s="14" t="n">
+        <v>656</v>
+      </c>
+      <c r="W37" s="15" t="n">
+        <v>1.8</v>
       </c>
       <c r="X37" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y37" s="9" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z37" s="10" t="inlineStr">
         <is>
-          <t>11:35 breakdown: 5m low 24,102.95 breached OR-30L 24,107.10 | 11:40 retest: 5m high 24,108.95 tested OR-30L 24,107.10 as resistance | 12:00 confirmation: 5m close 24,083.15 held below OR-30L and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
-        </is>
-      </c>
+          <t>09:45 breakout: 5m high 22,629.65 cleared PDH 22,621.80 | 09:50 retest: 5m low 22,611.75 tested PDH 22,621.80 as support | 09:55 confirmation: 5m close 22,642.50 held above PDH and VWAP</t>
+        </is>
+      </c>
+      <c r="AA37" s="10" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -4385,109 +4420,110 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30H Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>24169.1</v>
+        <v>22658.15</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>24202.1</v>
+        <v>22618.45</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>24070.1</v>
+        <v>22777.25</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>33</v>
+        <v>39.7</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>24169.1</v>
+        <v>22618.45</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>Breakeven</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="22" t="n">
-        <v>-0</v>
+        <v>-39.7</v>
+      </c>
+      <c r="O38" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24050 PE</t>
+          <t>NIFTY 22750 CE</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R38" s="4" t="n">
-        <v>70.95999999999999</v>
+        <v>146.03</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>70.09</v>
+        <v>129.6</v>
       </c>
       <c r="T38" s="6" t="n">
-        <v>13837</v>
+        <v>37968</v>
       </c>
       <c r="U38" s="6" t="n">
-        <v>13668</v>
-      </c>
-      <c r="V38" s="17" t="n">
-        <v>-242</v>
-      </c>
-      <c r="W38" s="18" t="n">
-        <v>-1.7</v>
+        <v>33696</v>
+      </c>
+      <c r="V38" s="20" t="n">
+        <v>-4384</v>
+      </c>
+      <c r="W38" s="21" t="n">
+        <v>-11.5</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y38" s="2" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>10:05 breakdown: 5m low 24,181.55 breached OR-30L 24,188.80 | 10:10 retest: 5m high 24,196.45 tested OR-30L 24,188.80 as resistance | 10:45 confirmation: 5m close 24,169.10 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>09:50 breakout: 5m high 22,637.70 cleared OR-30H 22,629.65 | 09:55 retest: 5m low 22,623.45 tested OR-30H 22,629.65 as support | 10:00 confirmation: 5m close 22,658.15 held above OR-30H and VWAP</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -4497,99 +4533,100 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>TRAILED (+1.11R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G39" s="11" t="n">
-        <v>24196.75</v>
+        <v>22575.8</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>24233.2</v>
+        <v>22611.75</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>24087.4</v>
+        <v>22467.95</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>36.45</v>
+        <v>35.95</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>24156.4</v>
+        <v>22611.75</v>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="M39" s="10" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="N39" s="11" t="n">
-        <v>40.35</v>
-      </c>
-      <c r="O39" s="12" t="n">
-        <v>1.11</v>
+        <v>-35.95</v>
+      </c>
+      <c r="O39" s="16" t="n">
+        <v>-1</v>
       </c>
       <c r="P39" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24100 PE</t>
+          <t>NIFTY 22500 PE</t>
         </is>
       </c>
       <c r="Q39" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R39" s="11" t="n">
-        <v>79.56999999999999</v>
+        <v>122.74</v>
       </c>
       <c r="S39" s="11" t="n">
-        <v>94.90000000000001</v>
+        <v>107.95</v>
       </c>
       <c r="T39" s="13" t="n">
-        <v>10344</v>
+        <v>23934</v>
       </c>
       <c r="U39" s="13" t="n">
-        <v>12337</v>
-      </c>
-      <c r="V39" s="14" t="n">
-        <v>1924</v>
-      </c>
-      <c r="W39" s="15" t="n">
-        <v>18.6</v>
+        <v>21050</v>
+      </c>
+      <c r="V39" s="17" t="n">
+        <v>-2972</v>
+      </c>
+      <c r="W39" s="18" t="n">
+        <v>-12.4</v>
       </c>
       <c r="X39" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y39" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z39" s="10" t="inlineStr">
         <is>
-          <t>09:30 breakdown: 5m low 24,198.40 breached PDL 24,207.75 | 09:35 retest: 5m high 24,211.70 tested PDL 24,207.75 as resistance | 10:00 confirmation: 5m close 24,196.75 held below PDL and VWAP</t>
-        </is>
-      </c>
+          <t>10:05 breakdown: 5m low 22,578.35 breached OR-30L 22,585.40 | 13:15 retest: 5m high 22,585.90 tested OR-30L 22,585.40 as resistance | 13:55 confirmation: 5m close 22,575.80 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA39" s="10" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4599,89 +4636,90 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+0.80R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>24303.1</v>
+        <v>22559.35</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>24337.65</v>
+        <v>22611.75</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>24147.62</v>
+        <v>22402.15</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>34.55</v>
+        <v>52.4</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>24275.35</v>
+        <v>22611.75</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="N40" s="4" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v>0.8</v>
+        <v>-52.4</v>
+      </c>
+      <c r="O40" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24200 PE</t>
+          <t>NIFTY 22450 PE</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R40" s="4" t="n">
-        <v>93.84999999999999</v>
+        <v>108.67</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>103.12</v>
+        <v>89.56</v>
       </c>
       <c r="T40" s="6" t="n">
-        <v>12200</v>
+        <v>21191</v>
       </c>
       <c r="U40" s="6" t="n">
-        <v>13406</v>
-      </c>
-      <c r="V40" s="7" t="n">
-        <v>1134</v>
-      </c>
-      <c r="W40" s="8" t="n">
-        <v>9.300000000000001</v>
+        <v>17464</v>
+      </c>
+      <c r="V40" s="20" t="n">
+        <v>-3808</v>
+      </c>
+      <c r="W40" s="21" t="n">
+        <v>-18</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y40" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>10:25 breakdown: 5m low 24,294.70 breached OR-30L 24,309.95 | 10:30 retest: 5m high 24,306.00 tested OR-30L 24,309.95 as resistance | 11:25 confirmation: 5m close 24,303.10 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>13:15 breakdown: 5m low 22,552.60 breached PDL 22,561.80 | 13:25 retest: 5m high 22,585.45 tested PDL 22,561.80 as resistance | 14:15 confirmation: 5m close 22,559.35 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -4691,109 +4729,110 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>PDH Support Flip [Tier 2 (Super-Trend]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>LONG</t>
+          <t>SHORT</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.90R)</t>
         </is>
       </c>
       <c r="G41" s="11" t="n">
-        <v>24371.6</v>
+        <v>22504.1</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>24336.1</v>
+        <v>22555.65</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>24478.1</v>
+        <v>22349.45</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>35.5</v>
+        <v>51.55</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>24336.1</v>
+        <v>22457.5</v>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="M41" s="10" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Structure Trail</t>
         </is>
       </c>
       <c r="N41" s="11" t="n">
-        <v>-35.5</v>
-      </c>
-      <c r="O41" s="23" t="n">
-        <v>-1</v>
+        <v>46.6</v>
+      </c>
+      <c r="O41" s="12" t="n">
+        <v>0.9</v>
       </c>
       <c r="P41" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24450 CE</t>
+          <t>NIFTY 22400 PE</t>
         </is>
       </c>
       <c r="Q41" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R41" s="11" t="n">
-        <v>105.33</v>
+        <v>102.9</v>
       </c>
       <c r="S41" s="11" t="n">
-        <v>91.06</v>
+        <v>121.28</v>
       </c>
       <c r="T41" s="13" t="n">
-        <v>13693</v>
+        <v>20066</v>
       </c>
       <c r="U41" s="13" t="n">
-        <v>11838</v>
-      </c>
-      <c r="V41" s="20" t="n">
-        <v>-1925</v>
-      </c>
-      <c r="W41" s="21" t="n">
-        <v>-14.1</v>
+        <v>23650</v>
+      </c>
+      <c r="V41" s="14" t="n">
+        <v>3495</v>
+      </c>
+      <c r="W41" s="15" t="n">
+        <v>17.4</v>
       </c>
       <c r="X41" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y41" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z41" s="10" t="inlineStr">
         <is>
-          <t>09:25 breakout: 5m high 24,355.85 cleared PDH 24,334.55 | 09:30 retest: 5m low 24,345.60 tested PDH 24,334.55 as support | 09:45 confirmation: 5m close 24,371.60 held above PDH and VWAP</t>
-        </is>
-      </c>
+          <t>09:20 breakdown: 5m low 22,521.70 breached PDL 22,546.55 | 09:25 retest: 5m high 22,550.65 tested PDL 22,546.55 as resistance | 09:30 confirmation: 5m close 22,504.10 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA41" s="10" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4803,191 +4842,193 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.47R)</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>24138.1</v>
+        <v>22456.9</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>24171.1</v>
+        <v>22503.1</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>24039.1</v>
+        <v>22318.3</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>33</v>
+        <v>46.2</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>24171.1</v>
+        <v>22435.3</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N42" s="4" t="n">
-        <v>-33</v>
-      </c>
-      <c r="O42" s="16" t="n">
-        <v>-1</v>
+        <v>21.6</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>0.47</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24050 PE</t>
+          <t>NIFTY 22350 PE</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R42" s="4" t="n">
-        <v>115.9</v>
+        <v>100.98</v>
       </c>
       <c r="S42" s="4" t="n">
-        <v>102.09</v>
+        <v>109.17</v>
       </c>
       <c r="T42" s="6" t="n">
-        <v>30134</v>
+        <v>19691</v>
       </c>
       <c r="U42" s="6" t="n">
-        <v>26543</v>
-      </c>
-      <c r="V42" s="17" t="n">
-        <v>-3689</v>
-      </c>
-      <c r="W42" s="18" t="n">
-        <v>-12.2</v>
+        <v>21288</v>
+      </c>
+      <c r="V42" s="7" t="n">
+        <v>1511</v>
+      </c>
+      <c r="W42" s="8" t="n">
+        <v>7.7</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y42" s="2" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t>09:20 breakdown: 5m low 24,129.15 breached PDL 24,144.45 | 09:50 retest: 5m high 24,166.10 tested PDL 24,144.45 as resistance | 09:55 confirmation: 5m close 24,138.10 held below PDL and VWAP</t>
-        </is>
-      </c>
+          <t>09:50 breakdown: 5m low 22,445.70 breached OR-30L 22,459.95 | 09:55 retest: 5m high 22,483.00 tested OR-30L 22,459.95 as resistance | 10:25 confirmation: 5m close 22,456.90 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 1 (General]</t>
+          <t>OR-30H Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>TRAILED (+0.32R)</t>
         </is>
       </c>
       <c r="G43" s="11" t="n">
-        <v>24179.3</v>
+        <v>22482.2</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>24209.4</v>
+        <v>22429.85</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>24089</v>
+        <v>22596.05</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>30.1</v>
+        <v>52.35</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>24179.3</v>
+        <v>22499.1</v>
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="M43" s="10" t="inlineStr">
         <is>
-          <t>Breakeven</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="19" t="n">
-        <v>-0</v>
+        <v>16.9</v>
+      </c>
+      <c r="O43" s="12" t="n">
+        <v>0.32</v>
       </c>
       <c r="P43" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24150 PE</t>
+          <t>NIFTY 22600 CE</t>
         </is>
       </c>
       <c r="Q43" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R43" s="11" t="n">
-        <v>47.42</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="S43" s="11" t="n">
-        <v>44.12</v>
+        <v>102.43</v>
       </c>
       <c r="T43" s="13" t="n">
-        <v>6165</v>
+        <v>18777</v>
       </c>
       <c r="U43" s="13" t="n">
-        <v>5736</v>
-      </c>
-      <c r="V43" s="20" t="n">
-        <v>-487</v>
-      </c>
-      <c r="W43" s="21" t="n">
-        <v>-7.9</v>
+        <v>19974</v>
+      </c>
+      <c r="V43" s="14" t="n">
+        <v>1114</v>
+      </c>
+      <c r="W43" s="15" t="n">
+        <v>5.9</v>
       </c>
       <c r="X43" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y43" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z43" s="10" t="inlineStr">
         <is>
-          <t>11:25 breakdown: 5m low 24,196.90 breached PDL 24,206.95 | 11:30 retest: 5m high 24,204.40 tested PDL 24,206.95 as resistance | 11:35 confirmation: 5m close 24,179.30 held below PDL and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
-        </is>
-      </c>
+          <t>09:50 breakout: 5m high 22,449.35 cleared OR-30H 22,433.25 | 09:55 retest: 5m low 22,434.85 tested OR-30H 22,433.25 as support | 10:10 confirmation: 5m close 22,482.20 held above OR-30H and VWAP</t>
+        </is>
+      </c>
+      <c r="AA43" s="10" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -4997,7 +5038,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5007,27 +5048,27 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+1.39R)</t>
+          <t>TRAILED (+0.77R)</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>24242.9</v>
+        <v>22506.15</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>24292.7</v>
+        <v>22538.7</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>24093.5</v>
+        <v>22359.68</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>49.8</v>
+        <v>32.55</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>24173.6</v>
+        <v>22481.05</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -5036,38 +5077,38 @@
         </is>
       </c>
       <c r="N44" s="4" t="n">
-        <v>69.3</v>
+        <v>25.1</v>
       </c>
       <c r="O44" s="5" t="n">
-        <v>1.39</v>
+        <v>0.77</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24150 PE</t>
+          <t>NIFTY 22400 PE</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="R44" s="4" t="n">
-        <v>26.03</v>
+        <v>33.27</v>
       </c>
       <c r="S44" s="4" t="n">
-        <v>47.95</v>
+        <v>40.3</v>
       </c>
       <c r="T44" s="6" t="n">
-        <v>5076</v>
+        <v>6488</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>9350</v>
+        <v>7858</v>
       </c>
       <c r="V44" s="7" t="n">
-        <v>4212</v>
+        <v>1310</v>
       </c>
       <c r="W44" s="8" t="n">
-        <v>83</v>
+        <v>20.2</v>
       </c>
       <c r="X44" s="2" t="n">
         <v>3</v>
@@ -5077,335 +5118,339 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t>10:00 breakdown: 5m low 24,267.30 breached OR-30L 24,272.55 | 10:05 retest: 5m high 24,276.55 tested OR-30L 24,272.55 as resistance | 11:00 confirmation: 5m close 24,242.90 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>09:55 breakdown: 5m low 22,472.15 breached OR-30L 22,508.40 | 10:00 retest: 5m high 22,527.40 tested OR-30L 22,508.40 as resistance | 10:05 confirmation: 5m close 22,506.15 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>PDH Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TARGET HIT (3R)</t>
         </is>
       </c>
       <c r="G45" s="11" t="n">
-        <v>24041.2</v>
+        <v>22787.2</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>24076.25</v>
+        <v>22739.35</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>23936.05</v>
+        <v>22930.75</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>35.05</v>
+        <v>47.85</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>24076.25</v>
+        <v>22930.75</v>
       </c>
       <c r="L45" s="9" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="M45" s="10" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="N45" s="11" t="n">
-        <v>-35.05</v>
-      </c>
-      <c r="O45" s="23" t="n">
-        <v>-1</v>
+        <v>143.55</v>
+      </c>
+      <c r="O45" s="12" t="n">
+        <v>2.5</v>
       </c>
       <c r="P45" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 23950 PE</t>
+          <t>NIFTY 22900 CE</t>
         </is>
       </c>
       <c r="Q45" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="R45" s="11" t="n">
-        <v>100.92</v>
+        <v>94.22</v>
       </c>
       <c r="S45" s="11" t="n">
-        <v>87.36</v>
+        <v>159.33</v>
       </c>
       <c r="T45" s="13" t="n">
-        <v>13120</v>
+        <v>18373</v>
       </c>
       <c r="U45" s="13" t="n">
-        <v>11357</v>
-      </c>
-      <c r="V45" s="20" t="n">
-        <v>-1832</v>
-      </c>
-      <c r="W45" s="21" t="n">
-        <v>-14</v>
+        <v>31069</v>
+      </c>
+      <c r="V45" s="14" t="n">
+        <v>12597</v>
+      </c>
+      <c r="W45" s="15" t="n">
+        <v>68.59999999999999</v>
       </c>
       <c r="X45" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y45" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z45" s="10" t="inlineStr">
         <is>
-          <t>10:25 breakdown: 5m low 24,063.20 breached OR-30L 24,065.50 | 10:30 retest: 5m high 24,071.25 tested OR-30L 24,065.50 as resistance | 11:10 confirmation: 5m close 24,041.20 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>09:35 breakout: 5m high 22,771.55 cleared PDH 22,757.80 | 09:40 retest: 5m low 22,748.55 tested PDH 22,757.80 as support | 09:50 confirmation: 5m close 22,787.20 held above PDH and VWAP</t>
+        </is>
+      </c>
+      <c r="AA45" s="10" t="n"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30H Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+0.22R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>24204.75</v>
+        <v>23109.55</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>24238.4</v>
+        <v>23072.2</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>24103.8</v>
+        <v>23221.6</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>33.65</v>
+        <v>37.35</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>24197.3</v>
+        <v>23072.2</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="N46" s="4" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v>0.22</v>
+        <v>-37.35</v>
+      </c>
+      <c r="O46" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24100 PE</t>
+          <t>NIFTY 23200 CE</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="R46" s="4" t="n">
-        <v>106.55</v>
+        <v>81.22</v>
       </c>
       <c r="S46" s="4" t="n">
-        <v>107.61</v>
+        <v>67.58</v>
       </c>
       <c r="T46" s="6" t="n">
-        <v>27703</v>
+        <v>15838</v>
       </c>
       <c r="U46" s="6" t="n">
-        <v>27979</v>
-      </c>
-      <c r="V46" s="7" t="n">
-        <v>177</v>
-      </c>
-      <c r="W46" s="8" t="n">
-        <v>0.6</v>
+        <v>13178</v>
+      </c>
+      <c r="V46" s="20" t="n">
+        <v>-2733</v>
+      </c>
+      <c r="W46" s="21" t="n">
+        <v>-17.3</v>
       </c>
       <c r="X46" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y46" s="2" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>10:05 breakdown: 5m low 24,213.00 breached PDL 24,226.95 | 10:10 retest: 5m high 24,228.40 tested PDL 24,226.95 as resistance | 10:50 confirmation: 5m close 24,204.75 held below PDL and VWAP</t>
-        </is>
-      </c>
+          <t>10:15 breakout: 5m high 23,094.60 cleared OR-30H 23,076.10 | 10:50 retest: 5m low 23,082.25 tested OR-30H 23,076.10 as support | 11:00 confirmation: 5m close 23,109.55 held above OR-30H and VWAP</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="n"/>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>PDH Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TRAILED (+0.99R)</t>
         </is>
       </c>
       <c r="G47" s="11" t="n">
-        <v>24252.8</v>
+        <v>23088.9</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>24288.9</v>
+        <v>23054.45</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>24144.5</v>
+        <v>23192.25</v>
       </c>
       <c r="J47" s="11" t="n">
-        <v>36.1</v>
+        <v>34.45</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>24288.9</v>
+        <v>23123.05</v>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="M47" s="10" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Structure Trail</t>
         </is>
       </c>
       <c r="N47" s="11" t="n">
-        <v>-36.1</v>
-      </c>
-      <c r="O47" s="23" t="n">
-        <v>-1</v>
+        <v>34.15</v>
+      </c>
+      <c r="O47" s="12" t="n">
+        <v>0.99</v>
       </c>
       <c r="P47" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24150 PE</t>
+          <t>NIFTY 23200 CE</t>
         </is>
       </c>
       <c r="Q47" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="R47" s="11" t="n">
-        <v>24.43</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="S47" s="11" t="n">
-        <v>14.9</v>
+        <v>85.19</v>
       </c>
       <c r="T47" s="13" t="n">
-        <v>6352</v>
+        <v>14303</v>
       </c>
       <c r="U47" s="13" t="n">
-        <v>3874</v>
-      </c>
-      <c r="V47" s="20" t="n">
-        <v>-2533</v>
-      </c>
-      <c r="W47" s="21" t="n">
-        <v>-39.9</v>
+        <v>16612</v>
+      </c>
+      <c r="V47" s="14" t="n">
+        <v>2232</v>
+      </c>
+      <c r="W47" s="15" t="n">
+        <v>15.6</v>
       </c>
       <c r="X47" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y47" s="9" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z47" s="10" t="inlineStr">
         <is>
-          <t>10:15 breakdown: 5m low 24,277.40 breached OR-30L 24,281.45 | 10:20 retest: 5m high 24,283.90 tested OR-30L 24,281.45 as resistance | 10:25 confirmation: 5m close 24,252.80 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>10:15 breakout: 5m high 23,094.60 cleared PDH 23,056.20 | 11:10 retest: 5m low 23,066.70 tested PDH 23,056.20 as support | 11:15 confirmation: 5m close 23,088.90 held above PDH and VWAP</t>
+        </is>
+      </c>
+      <c r="AA47" s="10" t="n"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5415,67 +5460,67 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+1.24R)</t>
+          <t>TRAILED (+0.38R)</t>
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>24283.85</v>
+        <v>22945.55</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>24317.45</v>
+        <v>22983.55</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>24183.05</v>
+        <v>22831.55</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>33.6</v>
+        <v>38</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>24242.1</v>
+        <v>22931.3</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>30-Min Stagnation Time-Stop (Theta Guard: 30m)</t>
         </is>
       </c>
       <c r="N48" s="4" t="n">
-        <v>41.75</v>
+        <v>14.25</v>
       </c>
       <c r="O48" s="5" t="n">
-        <v>1.24</v>
+        <v>0.38</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24200 PE</t>
+          <t>NIFTY 22850 PE</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="R48" s="4" t="n">
-        <v>30.17</v>
+        <v>147.75</v>
       </c>
       <c r="S48" s="4" t="n">
-        <v>43.62</v>
+        <v>153.49</v>
       </c>
       <c r="T48" s="6" t="n">
-        <v>5883</v>
+        <v>28811</v>
       </c>
       <c r="U48" s="6" t="n">
-        <v>8506</v>
+        <v>29931</v>
       </c>
       <c r="V48" s="7" t="n">
-        <v>2561</v>
+        <v>1017</v>
       </c>
       <c r="W48" s="8" t="n">
-        <v>43.5</v>
+        <v>3.5</v>
       </c>
       <c r="X48" s="2" t="n">
         <v>3</v>
@@ -5485,29 +5530,30 @@
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
-          <t>09:20 breakdown: 5m low 24,283.05 breached PDL 24,298.35 | 09:25 retest: 5m high 24,310.20 tested PDL 24,298.35 as resistance | 10:00 confirmation: 5m close 24,283.85 held below PDL and VWAP</t>
-        </is>
-      </c>
+          <t>12:05 breakdown: 5m low 22,948.75 breached OR-30L 22,970.85 | 12:10 retest: 5m high 22,978.55 tested OR-30L 22,970.85 as resistance | 12:15 confirmation: 5m close 22,945.55 held below OR-30L and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 3 Lots (195 Qty)]</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -5517,99 +5563,100 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>TARGET HIT (3R)</t>
+          <t>FLAT</t>
         </is>
       </c>
       <c r="G49" s="11" t="n">
-        <v>24375.65</v>
+        <v>22891.95</v>
       </c>
       <c r="H49" s="11" t="n">
-        <v>24405.95</v>
+        <v>22932.2</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>24284.75</v>
+        <v>22771.2</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>30.3</v>
+        <v>40.25</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>24284.75</v>
+        <v>22891.95</v>
       </c>
       <c r="L49" s="9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="M49" s="10" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Breakeven</t>
         </is>
       </c>
       <c r="N49" s="11" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="O49" s="12" t="n">
-        <v>2.5</v>
+        <v>0</v>
+      </c>
+      <c r="O49" s="22" t="n">
+        <v>-0</v>
       </c>
       <c r="P49" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24300 PE</t>
+          <t>NIFTY 22800 PE</t>
         </is>
       </c>
       <c r="Q49" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="R49" s="11" t="n">
-        <v>115.25</v>
+        <v>148.32</v>
       </c>
       <c r="S49" s="11" t="n">
-        <v>157.06</v>
+        <v>147.96</v>
       </c>
       <c r="T49" s="13" t="n">
-        <v>14982</v>
+        <v>28922</v>
       </c>
       <c r="U49" s="13" t="n">
-        <v>20418</v>
-      </c>
-      <c r="V49" s="14" t="n">
-        <v>5353</v>
-      </c>
-      <c r="W49" s="15" t="n">
-        <v>35.7</v>
+        <v>28852</v>
+      </c>
+      <c r="V49" s="17" t="n">
+        <v>-171</v>
+      </c>
+      <c r="W49" s="18" t="n">
+        <v>-0.6</v>
       </c>
       <c r="X49" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y49" s="9" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z49" s="10" t="inlineStr">
         <is>
-          <t>10:00 breakdown: 5m low 24,376.55 breached OR-30L 24,390.90 | 10:05 retest: 5m high 24,379.50 tested OR-30L 24,390.90 as resistance | 10:45 confirmation: 5m close 24,375.65 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>13:00 breakdown: 5m low 22,906.00 breached PDL 22,914.30 | 13:15 retest: 5m high 22,927.20 tested PDL 22,914.30 as resistance | 13:20 confirmation: 5m close 22,891.95 held below PDL and VWAP</t>
+        </is>
+      </c>
+      <c r="AA49" s="10" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30L Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -5619,99 +5666,100 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+1.37R)</t>
+          <t>STOPPED OUT (-1R)</t>
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>24428.2</v>
+        <v>22936.05</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>24468.5</v>
+        <v>22979.15</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>24307.3</v>
+        <v>22848.25</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>40.3</v>
+        <v>43.1</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>24373.1</v>
+        <v>22979.15</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>Stop</t>
         </is>
       </c>
       <c r="N50" s="4" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v>1.37</v>
+        <v>-43.1</v>
+      </c>
+      <c r="O50" s="19" t="n">
+        <v>-1</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24350 PE</t>
+          <t>NIFTY 22850 PE</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="R50" s="4" t="n">
-        <v>115.03</v>
+        <v>136.34</v>
       </c>
       <c r="S50" s="4" t="n">
-        <v>139.14</v>
+        <v>118.95</v>
       </c>
       <c r="T50" s="6" t="n">
-        <v>14954</v>
+        <v>26586</v>
       </c>
       <c r="U50" s="6" t="n">
-        <v>18088</v>
-      </c>
-      <c r="V50" s="7" t="n">
-        <v>3055</v>
-      </c>
-      <c r="W50" s="8" t="n">
-        <v>20.4</v>
+        <v>23195</v>
+      </c>
+      <c r="V50" s="20" t="n">
+        <v>-3483</v>
+      </c>
+      <c r="W50" s="21" t="n">
+        <v>-13.1</v>
       </c>
       <c r="X50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y50" s="2" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
-          <t>09:20 breakdown: 5m low 24,390.90 breached PDL 24,429.25 | 09:25 retest: 5m high 24,430.90 tested PDL 24,429.25 as resistance | 09:40 confirmation: 5m close 24,428.20 held below PDL and VWAP</t>
-        </is>
-      </c>
+          <t>10:10 breakdown: 5m low 22,950.90 breached OR-30L 22,981.35 | 10:15 retest: 5m high 22,974.15 tested OR-30L 22,981.35 as resistance | 10:20 confirmation: 5m close 22,936.05 held below OR-30L and VWAP</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (OR-30)</t>
+          <t>Breakout &amp; Retest (PD)</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>PDL Resistance Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -5721,129 +5769,130 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>FLAT</t>
+          <t>TARGET HIT (3R)</t>
         </is>
       </c>
       <c r="G51" s="11" t="n">
-        <v>24452</v>
+        <v>22818.45</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>24496.85</v>
+        <v>22850.55</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>24317.45</v>
+        <v>22722.15</v>
       </c>
       <c r="J51" s="11" t="n">
-        <v>44.85</v>
+        <v>32.1</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>24454.6</v>
+        <v>22722.15</v>
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="M51" s="10" t="inlineStr">
         <is>
-          <t>Time (15:10)</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="N51" s="11" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="O51" s="23" t="n">
-        <v>-0.06</v>
+        <v>96.3</v>
+      </c>
+      <c r="O51" s="12" t="n">
+        <v>2.5</v>
       </c>
       <c r="P51" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24350 PE</t>
+          <t>NIFTY 22700 PE</t>
         </is>
       </c>
       <c r="Q51" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="R51" s="11" t="n">
-        <v>121.22</v>
+        <v>121.21</v>
       </c>
       <c r="S51" s="11" t="n">
-        <v>118.25</v>
+        <v>162.55</v>
       </c>
       <c r="T51" s="13" t="n">
-        <v>31517</v>
+        <v>23636</v>
       </c>
       <c r="U51" s="13" t="n">
-        <v>30745</v>
-      </c>
-      <c r="V51" s="20" t="n">
-        <v>-877</v>
-      </c>
-      <c r="W51" s="21" t="n">
-        <v>-2.8</v>
+        <v>31697</v>
+      </c>
+      <c r="V51" s="14" t="n">
+        <v>7959</v>
+      </c>
+      <c r="W51" s="15" t="n">
+        <v>33.7</v>
       </c>
       <c r="X51" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y51" s="9" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z51" s="10" t="inlineStr">
         <is>
-          <t>09:50 breakdown: 5m low 24,464.15 breached OR-30L 24,468.40 | 09:55 retest: 5m high 24,477.45 tested OR-30L 24,468.40 as resistance | 11:05 confirmation: 5m close 24,452.00 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>11:40 breakdown: 5m low 22,839.70 breached PDL 22,845.25 | 11:45 retest: 5m high 22,841.90 tested PDL 22,845.25 as resistance | 11:55 confirmation: 5m close 22,818.45 held below PDL and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+        </is>
+      </c>
+      <c r="AA51" s="10" t="n"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Breakout &amp; Retest (PD)</t>
+          <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30H Support Flip [Preferred Lot Size: 4 Lots (260 Qty) [Super-Trend]]</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+1.18R)</t>
+          <t>TRAILED (+0.89R)</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>24481.75</v>
+        <v>22712.95</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>24513.3</v>
+        <v>22671.3</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>24387.1</v>
+        <v>22900.38</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>31.55</v>
+        <v>41.65</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>24444.65</v>
+        <v>22749.9</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -5852,60 +5901,61 @@
         </is>
       </c>
       <c r="N52" s="4" t="n">
-        <v>37.1</v>
+        <v>36.95</v>
       </c>
       <c r="O52" s="5" t="n">
-        <v>1.18</v>
+        <v>0.89</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24400 PE</t>
+          <t>NIFTY 22800 CE</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="R52" s="4" t="n">
-        <v>130.53</v>
+        <v>129.77</v>
       </c>
       <c r="S52" s="4" t="n">
-        <v>145.5</v>
+        <v>145.68</v>
       </c>
       <c r="T52" s="6" t="n">
-        <v>33938</v>
+        <v>25305</v>
       </c>
       <c r="U52" s="6" t="n">
-        <v>37830</v>
+        <v>28408</v>
       </c>
       <c r="V52" s="7" t="n">
-        <v>3776</v>
+        <v>3004</v>
       </c>
       <c r="W52" s="8" t="n">
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="X52" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y52" s="2" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
-          <t>09:20 breakdown: 5m low 24,501.00 breached PDL 24,511.30 | 09:25 retest: 5m high 24,506.35 tested PDL 24,511.30 as resistance | 09:40 confirmation: 5m close 24,481.75 held below PDL and VWAP</t>
-        </is>
-      </c>
+          <t>10:25 breakout: 5m high 22,742.50 cleared OR-30H 22,690.45 | 10:50 retest: 5m low 22,676.30 tested OR-30H 22,690.45 as support | 10:55 confirmation: 5m close 22,712.95 held above OR-30H and VWAP</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -5915,99 +5965,100 @@
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>OR-30L Resistance Flip [Tier 2 (Super-Trend]</t>
+          <t>OR-30 Breakout [1M Micro-Execution]</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>STOPPED OUT (-1R)</t>
+          <t>TARGET HIT (+3.59R)</t>
         </is>
       </c>
       <c r="G53" s="11" t="n">
-        <v>24582.4</v>
+        <v>22739.75</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>24628.2</v>
+        <v>22696.5</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>24431.2</v>
+        <v>22869.5</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>45.8</v>
+        <v>43.25</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>24628.2</v>
+        <v>22869.5</v>
       </c>
       <c r="L53" s="9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="M53" s="10" t="inlineStr">
         <is>
-          <t>Stop</t>
+          <t>Target (+3.0R Full Target Achieved)</t>
         </is>
       </c>
       <c r="N53" s="11" t="n">
-        <v>-45.8</v>
-      </c>
-      <c r="O53" s="23" t="n">
-        <v>-1</v>
+        <v>58.89</v>
+      </c>
+      <c r="O53" s="12" t="n">
+        <v>3.59</v>
       </c>
       <c r="P53" s="10" t="inlineStr">
         <is>
-          <t>NIFTY 24500 PE</t>
+          <t>NIFTY 22850 CE</t>
         </is>
       </c>
       <c r="Q53" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="R53" s="11" t="n">
-        <v>117.91</v>
+        <v>110.17</v>
       </c>
       <c r="S53" s="11" t="n">
-        <v>99.77</v>
+        <v>169.06</v>
       </c>
       <c r="T53" s="13" t="n">
-        <v>15328</v>
+        <v>28644</v>
       </c>
       <c r="U53" s="13" t="n">
-        <v>12970</v>
-      </c>
-      <c r="V53" s="20" t="n">
-        <v>-2431</v>
-      </c>
-      <c r="W53" s="21" t="n">
-        <v>-15.9</v>
+        <v>43955</v>
+      </c>
+      <c r="V53" s="14" t="n">
+        <v>15311</v>
+      </c>
+      <c r="W53" s="15" t="n">
+        <v>53.5</v>
       </c>
       <c r="X53" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y53" s="9" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Z53" s="10" t="inlineStr">
         <is>
-          <t>09:55 breakdown: 5m low 24,591.20 breached OR-30L 24,604.95 | 10:00 retest: 5m high 24,595.30 tested OR-30L 24,604.95 as resistance | 10:30 confirmation: 5m close 24,582.40 held below OR-30L and VWAP</t>
-        </is>
-      </c>
+          <t>09:34 1M candle closed at 22,739.75 clearing OR-30 high with volume expansion above VWAP. Exited on full target expansion to 22,869.50 (+58.89 pts / +3.59R).</t>
+        </is>
+      </c>
+      <c r="AA53" s="10" t="n"/>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -6017,194 +6068,307 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>PDL Resistance Flip [Tier 1 (General]</t>
+          <t>PDH Support Flip [15M Macro Structure]</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>TRAILED (+0.86R)</t>
+          <t>TARGET HIT (+3.47R)</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>24493.35</v>
+        <v>22827.05</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>24529.35</v>
+        <v>22782.3</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>24385.35</v>
+        <v>22961.3</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>36</v>
+        <v>44.75</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>24462.35</v>
+        <v>22958.2</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>Structure Trail</t>
+          <t>Target 3 Hit (+3.0R Full Target / 15:14 IST Spot 22,958+)</t>
         </is>
       </c>
       <c r="N54" s="4" t="n">
-        <v>31</v>
+        <v>59.53</v>
       </c>
       <c r="O54" s="5" t="n">
-        <v>0.86</v>
+        <v>3.47</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>NIFTY 24450 PE</t>
+          <t>NIFTY 22950 CE</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="R54" s="4" t="n">
-        <v>141.85</v>
+        <v>99.08</v>
       </c>
       <c r="S54" s="4" t="n">
-        <v>155.69</v>
+        <v>158.61</v>
       </c>
       <c r="T54" s="6" t="n">
-        <v>27661</v>
+        <v>25761</v>
       </c>
       <c r="U54" s="6" t="n">
-        <v>30360</v>
+        <v>41239</v>
       </c>
       <c r="V54" s="7" t="n">
-        <v>2596</v>
+        <v>15478</v>
       </c>
       <c r="W54" s="8" t="n">
-        <v>9.4</v>
+        <v>60.1</v>
       </c>
       <c r="X54" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y54" s="2" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="Z54" s="3" t="inlineStr">
         <is>
-          <t>12:05 breakdown: 5m low 24,505.55 breached PDL 24,515.50 | 12:10 retest: 5m high 24,524.05 tested PDL 24,515.50 as resistance | 12:45 confirmation: 5m close 24,493.35 held below PDL and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
-        </is>
-      </c>
+          <t>11:15 IST 15M breakout and retest of PDH held above VWAP. Reached full target at 15:14 IST (+59.53 pts / +3.47R). Realized +Rs 15,478.00.</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="n"/>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
+          <t>Breakout &amp; Retest (PD)</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>PDH Support Flip [5M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.14R)</t>
+        </is>
+      </c>
+      <c r="G55" s="11" t="n">
+        <v>22980.7</v>
+      </c>
+      <c r="H55" s="11" t="n">
+        <v>22950.1</v>
+      </c>
+      <c r="I55" s="11" t="n">
+        <v>23072.5</v>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="K55" s="11" t="n">
+        <v>23053.45</v>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="M55" s="10" t="inlineStr">
+        <is>
+          <t>+3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="N55" s="11" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="O55" s="12" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P55" s="10" t="inlineStr">
+        <is>
+          <t>NIFTY 23100 CE</t>
+        </is>
+      </c>
+      <c r="Q55" s="9" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R55" s="11" t="n">
+        <v>78.67</v>
+      </c>
+      <c r="S55" s="11" t="n">
+        <v>114.32</v>
+      </c>
+      <c r="T55" s="13" t="n">
+        <v>20454</v>
+      </c>
+      <c r="U55" s="13" t="n">
+        <v>29723</v>
+      </c>
+      <c r="V55" s="14" t="n">
+        <v>9269</v>
+      </c>
+      <c r="W55" s="15" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="X55" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y55" s="9" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z55" s="10" t="inlineStr">
+        <is>
+          <t>Paper trading forward test executed on 5M timeframe. +3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="AA55" s="10" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
           <t>Breakout &amp; Retest (OR-30)</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>OR-30L Resistance Flip [Tier 1 (General]</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>SHORT</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>TRAILED (+1.70R)</t>
-        </is>
-      </c>
-      <c r="G55" s="11" t="n">
-        <v>24568.8</v>
-      </c>
-      <c r="H55" s="11" t="n">
-        <v>24603.8</v>
-      </c>
-      <c r="I55" s="11" t="n">
-        <v>24463.8</v>
-      </c>
-      <c r="J55" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="K55" s="11" t="n">
-        <v>24519.75</v>
-      </c>
-      <c r="L55" s="9" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="M55" s="10" t="inlineStr">
-        <is>
-          <t>Partial + Structure Trail</t>
-        </is>
-      </c>
-      <c r="N55" s="11" t="n">
-        <v>49.05</v>
-      </c>
-      <c r="O55" s="12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P55" s="10" t="inlineStr">
-        <is>
-          <t>NIFTY 24500 PE</t>
-        </is>
-      </c>
-      <c r="Q55" s="9" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="R55" s="11" t="n">
-        <v>131.48</v>
-      </c>
-      <c r="S55" s="11" t="n">
-        <v>153.37</v>
-      </c>
-      <c r="T55" s="13" t="n">
-        <v>25639</v>
-      </c>
-      <c r="U55" s="13" t="n">
-        <v>29907</v>
-      </c>
-      <c r="V55" s="14" t="n">
-        <v>4168</v>
-      </c>
-      <c r="W55" s="15" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="X55" s="9" t="n">
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>OR-30H Support Flip [5M Micro-Execution]</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>TARGET HIT (+3.34R)</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>23006.25</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>22974.75</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>23100.75</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>23053.1</v>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>+3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>NIFTY 23100 CE</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="R56" s="4" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="S56" s="4" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="T56" s="6" t="n">
+        <v>16190</v>
+      </c>
+      <c r="U56" s="6" t="n">
+        <v>25610</v>
+      </c>
+      <c r="V56" s="7" t="n">
+        <v>9420</v>
+      </c>
+      <c r="W56" s="8" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="X56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Y55" s="9" t="n">
-        <v>195</v>
-      </c>
-      <c r="Z55" s="10" t="inlineStr">
-        <is>
-          <t>10:35 breakdown: 5m low 24,581.00 breached OR-30L 24,589.80 | 10:40 retest: 5m high 24,586.25 tested OR-30L 24,589.80 as resistance | 11:35 confirmation: 5m close 24,568.80 held below OR-30L and VWAP | [Midday Waterfall Active (Tier parameters satisfied)]</t>
+      <c r="Y56" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>Paper trading forward test executed on 5M timeframe. +3.0R Full Marathon Target Achieved</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>paper</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z55"/>
+  <autoFilter ref="A1:AA56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>